--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t xml:space="preserve">date_local</t>
   </si>
@@ -86,412 +86,265 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">south sydney rabbitohs v newcastle knights</t>
+    <t xml:space="preserve">sydney roosters v cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_centre 1.51 (off 1.42 x def 1.07): KL Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_wing 1.28 (off 1.19 x def 1.07): Mark Nawaqanitawase; right_centre 1.37 (off 1.07 x def 1.28): Billy Smith; right_wing 1.31 (off 1.17 x def 1.12): Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors v newcastle knights</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_wing 1.28 (off 1.13 x def 1.13): Greg Marzhew; left_centre 1.29 (off 0.89 x def 1.46): Bradman Best; right_wing 1.15 (off 1.21 x def 0.96): Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right_centre 1.26 (off 0.91 x def 1.38): Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_expected_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_attack_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_conceded_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_defence_conceded_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_concede_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_concede_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matchup_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_channel_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matchup_signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focus_player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focus_player_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260919-1950-sydney-roosters-cronulla-sutherland-sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KL Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KL Iro (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy (last 2026-09-12, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Jones (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco (last 2026-09-13, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260920-1805-warriors-newcastle-knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew (last 2026-09-11, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best (last 2026-09-11, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga (last 2026-09-11, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai (last 2026-09-11, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young (last 2026-09-11, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey (last 2026-09-12, bench_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki (last 2026-09-12, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">away</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fullback 1.29 (off 0.97 x def 1.33): Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_centre 1.94 (off 1.42 x def 1.36): Latrell Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors v dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_centre 1.97 (off 1.37 x def 1.44): Herbie Farnworth; fullback 1.63 (off 1.56 x def 1.05): Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No wing/centre/fullback focus &gt;= 1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks v north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_centre 1.51 (off 1.24 x def 1.21): Jaxon Purdue; right_wing 1.15 (off 1.02 x def 1.13): Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.17 (off 0.90 x def 1.30): Ronaldo Mulitalo; left_centre 1.30 (off 1.40 x def 0.93): Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers v sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_centre 1.46 (off 1.12 x def 1.30): Fetalaiga Pauga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_centre 1.51 (off 1.41 x def 1.07): Casey McLean; right_wing 1.32 (off 1.35 x def 0.98): Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_expected_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_attack_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_conceded_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_defence_conceded_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_concede_share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_concede_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matchup_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected_channel_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matchup_signal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">focus_player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">focus_player_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260911-1950-south-sydney-rabbitohs-newcastle-knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neutral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga (last 2026-08-30, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray (last 2026-09-04, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrell Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrell Mitchell (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260912-1805-warriors-dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Naufahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Naufahu (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow (last 2026-09-04, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey (last 2026-09-05, bench_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad (last 2026-09-05, bench_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Laulilii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Laulilii (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260912-1950-cronulla-sutherland-sharks-north-queensland-cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai (last 2026-09-05, bench_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy (last 2026-09-05, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Jones (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Derby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Derby (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater (last 2026-09-05, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns (last 2026-09-05, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260913-1605-penrith-panthers-sydney-roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o (last 2026-09-06, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean (last 2026-09-06, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards (last 2026-09-06, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner (last 2026-09-06, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins (last 2026-09-06, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rex Bassingthwaighte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rex Bassingthwaighte (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Talau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Talau (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey (last 2026-09-04, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetalaiga Pauga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetalaiga Pauga (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou (last 2026-09-04, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
@@ -890,7 +743,7 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="46.1575" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="38.44" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="4.14" hidden="0" customWidth="1"/>
@@ -909,7 +762,7 @@
     <col min="19" max="19" width="9.285" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="12.715" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="98.465" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="141.34" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -982,7 +835,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -1000,49 +853,49 @@
         <v>26</v>
       </c>
       <c r="G2" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="T2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>1.21</v>
-      </c>
       <c r="U2" s="4" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -1050,7 +903,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -1068,49 +921,49 @@
         <v>28</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.73</v>
+        <v>1.28</v>
       </c>
       <c r="H3" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="I3" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>1.09</v>
-      </c>
       <c r="P3" s="4" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.65</v>
+        <v>1.12</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>29</v>
@@ -1118,7 +971,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -1136,49 +989,49 @@
         <v>26</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>1.13</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1.37</v>
+        <v>0.89</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1.56</v>
+        <v>0.95</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.88</v>
+        <v>1.15</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>0.91</v>
+        <v>1.21</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>34</v>
@@ -1186,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>30</v>
@@ -1204,328 +1057,56 @@
         <v>28</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.1</v>
+        <v>0.94</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0.65</v>
       </c>
       <c r="L5" s="4" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O5" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0.9</v>
-      </c>
       <c r="P5" s="4" t="n">
-        <v>0.94</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.82</v>
+        <v>0.56</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.89</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:S9">
+  <conditionalFormatting sqref="G2:S5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1549,8 +1130,8 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="65.88" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="46.1575" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="58.1625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="38.44" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="4.14" hidden="0" customWidth="1"/>
@@ -1568,7 +1149,7 @@
     <col min="19" max="19" width="19.575" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="20.4325" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="53.0175" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="54.7325" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1579,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1594,60 +1175,60 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>23</v>
@@ -1662,60 +1243,60 @@
         <v>26</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.9477</v>
+        <v>4.2401</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.1833</v>
+        <v>0.1429</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>1.1421</v>
+        <v>0.8853</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1402</v>
+        <v>0.1355</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.8735</v>
+        <v>0.8392</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.9977</v>
+        <v>0.7429</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.8017</v>
+        <v>0.4984</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>23</v>
@@ -1730,60 +1311,60 @@
         <v>26</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.9477</v>
+        <v>4.2401</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.0851</v>
+        <v>0.1349</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.9003</v>
+        <v>1.415</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.0895</v>
+        <v>0.102</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.9467</v>
+        <v>1.0704</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.8523</v>
+        <v>1.5146</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.4034</v>
+        <v>0.5999</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>23</v>
@@ -1798,60 +1379,60 @@
         <v>26</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4.9477</v>
+        <v>4.2401</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0958</v>
+        <v>0.0805</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.9717</v>
+        <v>0.8055</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1311</v>
+        <v>0.1166</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1.3302</v>
+        <v>1.1671</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.2926</v>
+        <v>0.9402</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.6377</v>
+        <v>0.3903</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>23</v>
@@ -1866,60 +1447,60 @@
         <v>26</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4.9477</v>
+        <v>4.2401</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0603</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.6536</v>
+        <v>0.6672</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.0617</v>
+        <v>0.0732</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.6833</v>
+        <v>0.8095</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.4465</v>
+        <v>0.5401</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.2018</v>
+        <v>0.203</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
@@ -1934,60 +1515,60 @@
         <v>26</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.9477</v>
+        <v>4.2401</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.15</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.2104</v>
+        <v>0.9984</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.1488</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.8946</v>
+        <v>0.9905</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.0828</v>
+        <v>0.9889</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.8175</v>
+        <v>0.6176</v>
       </c>
       <c r="T6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="U6" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="V6" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>23</v>
@@ -2002,60 +1583,60 @@
         <v>28</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.4423</v>
+        <v>4.4997</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.1928</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.8297</v>
+        <v>1.1943</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1405</v>
+        <v>0.1734</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.875</v>
+        <v>1.0741</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.726</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.624</v>
+        <v>0.9182</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>23</v>
@@ -2070,60 +1651,60 @@
         <v>28</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.4423</v>
+        <v>4.4997</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0474</v>
+        <v>0.0973</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5009</v>
+        <v>1.0211</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0649</v>
+        <v>0.0831</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.6865</v>
+        <v>0.8715</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.3439</v>
+        <v>0.8899</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1741</v>
+        <v>0.3761</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>23</v>
@@ -2138,60 +1719,60 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.4423</v>
+        <v>4.4997</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0747</v>
+        <v>0.1055</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7577</v>
+        <v>1.0567</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.107</v>
+        <v>0.0834</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.086</v>
+        <v>0.835</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8229</v>
+        <v>0.8823</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.4342</v>
+        <v>0.3908</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>23</v>
@@ -2206,60 +1787,60 @@
         <v>28</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.4423</v>
+        <v>4.4997</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1281</v>
+        <v>0.097</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.4195</v>
+        <v>1.0727</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1232</v>
+        <v>0.1159</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.3649</v>
+        <v>1.2811</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.9375</v>
+        <v>1.3742</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.9364</v>
+        <v>0.5511</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>23</v>
@@ -2274,60 +1855,60 @@
         <v>28</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.4423</v>
+        <v>4.4997</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2361</v>
+        <v>0.1762</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.5655</v>
+        <v>1.1727</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.098</v>
+        <v>0.1678</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6496</v>
+        <v>1.1167</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.0169</v>
+        <v>1.3095</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.8211</v>
+        <v>0.8725</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>31</v>
@@ -2342,60 +1923,60 @@
         <v>26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.3236</v>
+        <v>4.0539</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1497</v>
+        <v>0.1825</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9324</v>
+        <v>1.1304</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1809</v>
+        <v>0.1825</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.1271</v>
+        <v>1.1307</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.051</v>
+        <v>1.2782</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.7132</v>
+        <v>0.8347</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>31</v>
@@ -2410,60 +1991,60 @@
         <v>26</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.3236</v>
+        <v>4.0539</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1295</v>
+        <v>0.0847</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.3701</v>
+        <v>0.8892</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1362</v>
+        <v>0.1387</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.4404</v>
+        <v>1.4555</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.9735</v>
+        <v>1.2942</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.7887</v>
+        <v>0.499</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>31</v>
@@ -2478,60 +2059,60 @@
         <v>26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.3236</v>
+        <v>4.0539</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1537</v>
+        <v>0.0954</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.5596</v>
+        <v>0.9548</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1032</v>
+        <v>0.1065</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.0473</v>
+        <v>1.0663</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.6334</v>
+        <v>1.0182</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.6804</v>
+        <v>0.4114</v>
       </c>
       <c r="T14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>31</v>
@@ -2546,60 +2127,60 @@
         <v>26</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.3236</v>
+        <v>4.0539</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.7058</v>
+      </c>
+      <c r="N15" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>235</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.0735</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0.8141</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="O15" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.0969</v>
+        <v>0.1003</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.0737</v>
+        <v>1.1085</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.8741</v>
+        <v>0.7824</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.3335</v>
+        <v>0.2863</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
@@ -2614,60 +2195,60 @@
         <v>26</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.3236</v>
+        <v>4.0539</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1371</v>
+        <v>0.1816</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9091</v>
+        <v>1.2083</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>24</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1467</v>
+        <v>0.1435</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.973</v>
+        <v>0.955</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.8845</v>
+        <v>1.154</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.5639</v>
+        <v>0.7015</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>31</v>
@@ -2682,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.1812</v>
+        <v>5.222</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>6</v>
@@ -2691,51 +2272,51 @@
         <v>38</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1726</v>
+        <v>0.172</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.0754</v>
+        <v>1.0653</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1646</v>
+        <v>0.1423</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.0255</v>
+        <v>0.8816</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.1028</v>
+        <v>0.9391</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.9168</v>
+        <v>0.7713</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>31</v>
@@ -2750,7 +2331,7 @@
         <v>28</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.1812</v>
+        <v>5.222</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>9</v>
@@ -2759,51 +2340,51 @@
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0618</v>
+        <v>0.0615</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6532</v>
+        <v>0.6458</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1072</v>
+        <v>0.0658</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.1339</v>
+        <v>0.6902</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.7407</v>
+        <v>0.4457</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.3627</v>
+        <v>0.2162</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>31</v>
@@ -2818,60 +2399,60 @@
         <v>28</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.1812</v>
+        <v>5.222</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.0705</v>
+        <v>0.0746</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.7158</v>
+        <v>0.7465</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.0885</v>
+        <v>0.1127</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.8977</v>
+        <v>1.1283</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.6426</v>
+        <v>0.8423</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3279</v>
+        <v>0.4281</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>31</v>
@@ -2886,7 +2467,7 @@
         <v>28</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.1812</v>
+        <v>5.222</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
@@ -2895,51 +2476,51 @@
         <v>18</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0827</v>
+        <v>0.0824</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9167</v>
+        <v>0.9111</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.0926</v>
+        <v>0.1248</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.0258</v>
+        <v>1.3796</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.9404</v>
+        <v>1.257</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4396</v>
+        <v>0.5785</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>31</v>
@@ -2954,7 +2535,7 @@
         <v>28</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.1812</v>
+        <v>5.222</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>18</v>
@@ -2963,1400 +2544,40 @@
         <v>29</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1337</v>
+        <v>0.1331</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8863</v>
+        <v>0.8856</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1401</v>
+        <v>0.0949</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.9287</v>
+        <v>0.6318</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.8231</v>
+        <v>0.5595</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6429</v>
+        <v>0.4278</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>5.9328</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.1445</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0.9004</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>0.2084</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>1.2985</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>1.1692</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>1.1185</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>5.9328</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.1325</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>1.401</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>0.0876</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>0.9265</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>1.2981</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>0.7314</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>5.9328</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0.0774</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0.7852</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>0.0917</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>0.9309</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>0.4293</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>5.9328</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>0.6763</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>0.0795</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>0.8813</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>0.5961</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0.3206</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V25" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>5.9328</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0.1479</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0.9805</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>0.1339</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0.8879</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>0.8706</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>0.7825</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>3.8478</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0.1586</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>0.9878</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>0.1662</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>1.0354</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>1.0228</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>0.6391</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>3.8478</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>0.0803</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>0.8497</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>0.0818</v>
-      </c>
-      <c r="Q28" s="4" t="n">
-        <v>0.8656</v>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>0.7355</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>0.2707</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="V28" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>3.8478</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>0.1036</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>1.0509</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>0.0821</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>0.8335</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0.8759</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>3.8478</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.1121</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>1.2423</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>0.1096</v>
-      </c>
-      <c r="Q30" s="4" t="n">
-        <v>1.2137</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>0.5297</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="V30" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>3.8478</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.1533</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>1.0163</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>0.1702</v>
-      </c>
-      <c r="Q31" s="4" t="n">
-        <v>1.1282</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>1.1466</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>0.6731</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="V31" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>4.3032</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>0.1534</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>0.9554</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>0.1341</v>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>0.8355</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>0.7983</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>0.5466</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>4.3032</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>0.1338</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>1.4149</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>1.0683</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>1.5115</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>0.6096</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>4.3032</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>0.0875</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v>0.1107</v>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>1.1232</v>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>0.9974</v>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>0.4193</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>4.3032</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>0.6632</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>0.0772</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>0.8553</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>0.5673</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>0.2184</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>4.3032</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>0.2032</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>1.347</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>0.9779</v>
-      </c>
-      <c r="R36" s="4" t="n">
-        <v>1.3172</v>
-      </c>
-      <c r="S36" s="4" t="n">
-        <v>0.8474</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>3.9777</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>0.1888</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>1.1759</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>0.1469</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>0.9154</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>1.0764</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>0.7079</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="V37" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>3.9777</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>0.0933</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>0.9869</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0.0834</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>0.8822</v>
-      </c>
-      <c r="R38" s="4" t="n">
-        <v>0.8706</v>
-      </c>
-      <c r="S38" s="4" t="n">
-        <v>0.3372</v>
-      </c>
-      <c r="T38" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V38" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>3.9777</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>0.1094</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>1.1105</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>0.0895</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>0.9084</v>
-      </c>
-      <c r="R39" s="4" t="n">
-        <v>1.0088</v>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>0.4073</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="V39" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>3.9777</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>1.1186</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v>0.1175</v>
-      </c>
-      <c r="Q40" s="4" t="n">
-        <v>1.3017</v>
-      </c>
-      <c r="R40" s="4" t="n">
-        <v>1.4562</v>
-      </c>
-      <c r="S40" s="4" t="n">
-        <v>0.5385</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="V40" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>3.9777</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0.1762</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>1.1686</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>0.1058</v>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>0.7017</v>
-      </c>
-      <c r="R41" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="S41" s="4" t="n">
-        <v>0.5066</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4384,39 +2605,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -4428,10 +2649,10 @@
         <v>209</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1447</v>
+        <v>0.1448</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.9017</v>
+        <v>0.8971</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>25</v>
@@ -4443,12 +2664,12 @@
         <v>0.1199</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.7467</v>
+        <v>0.7429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -4460,10 +2681,10 @@
         <v>209</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.1179</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.2463</v>
+        <v>1.2369</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>21</v>
@@ -4475,12 +2696,12 @@
         <v>0.0979</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.0353</v>
+        <v>1.0276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
@@ -4492,10 +2713,10 @@
         <v>209</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1092</v>
+        <v>0.1093</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.1084</v>
+        <v>1.0945</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>27</v>
@@ -4504,15 +2725,15 @@
         <v>214</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.1242</v>
+        <v>0.1243</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.2608</v>
+        <v>1.2448</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
@@ -4527,7 +2748,7 @@
         <v>0.0998</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1052</v>
+        <v>1.1031</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>21</v>
@@ -4539,12 +2760,12 @@
         <v>0.0976</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.0811</v>
+        <v>1.0791</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>18</v>
@@ -4556,10 +2777,10 @@
         <v>209</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1352</v>
+        <v>0.1351</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.8963</v>
+        <v>0.8993</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>37</v>
@@ -4568,15 +2789,15 @@
         <v>214</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1714</v>
+        <v>0.1713</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.1362</v>
+        <v>1.1402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -4588,10 +2809,10 @@
         <v>220</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1253</v>
+        <v>0.1254</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.7805</v>
+        <v>0.7766</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>38</v>
@@ -4600,15 +2821,15 @@
         <v>206</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1827</v>
+        <v>0.1828</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.1384</v>
+        <v>1.1325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -4620,10 +2841,10 @@
         <v>220</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.0742</v>
+        <v>0.0743</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7849</v>
+        <v>0.7792</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>25</v>
@@ -4632,15 +2853,15 @@
         <v>206</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1194</v>
+        <v>0.1195</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.2632</v>
+        <v>1.2537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -4652,10 +2873,10 @@
         <v>220</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1211</v>
+        <v>0.1212</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.2288</v>
+        <v>1.2132</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>17</v>
@@ -4664,15 +2885,15 @@
         <v>206</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0837</v>
+        <v>0.0838</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8492</v>
+        <v>0.8387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>15</v>
@@ -4687,7 +2908,7 @@
         <v>0.1078</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.1945</v>
+        <v>1.1922</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>16</v>
@@ -4699,12 +2920,12 @@
         <v>0.0786</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8706</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
@@ -4719,7 +2940,7 @@
         <v>0.1119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7421</v>
+        <v>0.7446</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>28</v>
@@ -4731,76 +2952,76 @@
         <v>0.137</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9084</v>
+        <v>0.9115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1378</v>
+        <v>0.1356</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8587</v>
+        <v>0.8402</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>38</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2039</v>
+        <v>0.2081</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2893</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0726</v>
+        <v>0.069</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7675</v>
+        <v>0.724</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.0579</v>
+        <v>0.0591</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6119</v>
+        <v>0.6201</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -4809,30 +3030,30 @@
         <v>11</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.0629</v>
+        <v>0.0643</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6381</v>
+        <v>0.6435</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0697</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6923</v>
+        <v>0.6981</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>15</v>
@@ -4841,62 +3062,62 @@
         <v>16</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.0872</v>
+        <v>0.089</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.9842</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0587</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6928</v>
+        <v>0.6491</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1271</v>
+        <v>0.1245</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8425</v>
+        <v>0.8286</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2131</v>
+        <v>0.2123</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.4132</v>
+        <v>1.4131</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -4905,94 +3126,94 @@
         <v>34</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1445</v>
+        <v>0.1429</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9004</v>
+        <v>0.8853</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1662</v>
+        <v>0.1734</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.0354</v>
+        <v>1.0741</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1325</v>
+        <v>0.1349</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.401</v>
+        <v>1.415</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0818</v>
+        <v>0.0831</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8656</v>
+        <v>0.8715</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.0805</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7852</v>
+        <v>0.8055</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0821</v>
+        <v>0.0834</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8335</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>15</v>
@@ -5001,190 +3222,190 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.061</v>
+        <v>0.0603</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6763</v>
+        <v>0.6672</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1159</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.2137</v>
+        <v>1.2811</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1479</v>
+        <v>0.15</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9805</v>
+        <v>0.9984</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1702</v>
+        <v>0.1678</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.1282</v>
+        <v>1.1167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1497</v>
+        <v>0.1513</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9324</v>
+        <v>0.9373</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>32</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1646</v>
+        <v>0.1639</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.0255</v>
+        <v>1.0154</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1295</v>
+        <v>0.1315</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.3701</v>
+        <v>1.3795</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1072</v>
+        <v>0.1068</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.1339</v>
+        <v>1.1201</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1537</v>
+        <v>0.1553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.5596</v>
+        <v>1.5546</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.0885</v>
+        <v>0.0929</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8977</v>
+        <v>0.9299</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0735</v>
+        <v>0.0763</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8141</v>
+        <v>0.8432</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.0926</v>
+        <v>0.0922</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.0258</v>
+        <v>1.0191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>18</v>
@@ -5193,30 +3414,30 @@
         <v>32</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1371</v>
+        <v>0.1349</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9091</v>
+        <v>0.8979</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1401</v>
+        <v>0.1394</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9287</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
@@ -5228,10 +3449,10 @@
         <v>176</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1748</v>
+        <v>0.1749</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.0891</v>
+        <v>1.0836</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>39</v>
@@ -5240,15 +3461,15 @@
         <v>243</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1605</v>
+        <v>0.1606</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9998</v>
+        <v>0.9946</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -5260,10 +3481,10 @@
         <v>176</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1068</v>
+        <v>0.1069</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.13</v>
+        <v>1.1217</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>20</v>
@@ -5275,12 +3496,12 @@
         <v>0.0831</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8785</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>12</v>
@@ -5292,10 +3513,10 @@
         <v>176</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.0448</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4533</v>
+        <v>0.4483</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>24</v>
@@ -5307,12 +3528,12 @@
         <v>0.0988</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.0021</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>15</v>
@@ -5327,7 +3548,7 @@
         <v>0.0909</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.0066</v>
+        <v>1.0047</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>26</v>
@@ -5339,12 +3560,12 @@
         <v>0.106</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.174</v>
+        <v>1.1717</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>18</v>
@@ -5356,10 +3577,10 @@
         <v>176</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1272</v>
+        <v>0.1271</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8431</v>
+        <v>0.8459</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>34</v>
@@ -5371,12 +3592,12 @@
         <v>0.1406</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9322</v>
+        <v>0.9354</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
@@ -5385,30 +3606,30 @@
         <v>38</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1764</v>
+        <v>0.1796</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.1124</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1694</v>
+        <v>0.1679</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.0551</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
@@ -5417,30 +3638,30 @@
         <v>22</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1022</v>
+        <v>0.1041</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.0813</v>
+        <v>1.0922</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.0834</v>
+        <v>0.0802</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8821</v>
+        <v>0.8417</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>12</v>
@@ -5449,94 +3670,94 @@
         <v>19</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.0895</v>
+        <v>0.0911</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9079</v>
+        <v>0.9125</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1075</v>
+        <v>0.1097</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.091</v>
+        <v>1.0983</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1498</v>
+        <v>0.148</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.6592</v>
+        <v>1.6364</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.0735</v>
+        <v>0.075</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.8148</v>
+        <v>0.8291</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.1279</v>
+        <v>0.1257</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.8479</v>
+        <v>0.8364</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.1591</v>
+        <v>0.1573</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.055</v>
+        <v>1.0469</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>6</v>
@@ -5545,30 +3766,30 @@
         <v>39</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.1569</v>
+        <v>0.1606</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.9772</v>
+        <v>0.9946</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>38</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.1844</v>
+        <v>0.1862</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1487</v>
+        <v>1.1533</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
@@ -5577,30 +3798,30 @@
         <v>18</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.0736</v>
+        <v>0.0754</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7788</v>
+        <v>0.791</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.1023</v>
+        <v>0.1033</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.0824</v>
+        <v>1.0841</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>12</v>
@@ -5609,30 +3830,30 @@
         <v>38</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.1493</v>
+        <v>0.1529</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.5155</v>
+        <v>1.5306</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.0799</v>
+        <v>0.0807</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.8108</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>15</v>
@@ -5641,62 +3862,62 @@
         <v>13</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0545</v>
+        <v>0.0558</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.6039</v>
+        <v>0.6168</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.0884</v>
+        <v>0.0892</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.9792</v>
+        <v>0.9864</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.145</v>
+        <v>0.1406</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.9611</v>
+        <v>0.9354</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0.1837</v>
+        <v>0.1808</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.218</v>
+        <v>1.203</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>6</v>
@@ -5705,30 +3926,30 @@
         <v>33</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.1833</v>
+        <v>0.1825</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.1421</v>
+        <v>1.1304</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>31</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.1405</v>
+        <v>0.1423</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.875</v>
+        <v>0.8816</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>9</v>
@@ -5737,30 +3958,30 @@
         <v>15</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.0851</v>
+        <v>0.0847</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.9003</v>
+        <v>0.8892</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.0649</v>
+        <v>0.0658</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.6865</v>
+        <v>0.6902</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>12</v>
@@ -5769,62 +3990,62 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.0958</v>
+        <v>0.0954</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.9717</v>
+        <v>0.9548</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.107</v>
+        <v>0.1127</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.086</v>
+        <v>1.1283</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0638</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.6536</v>
+        <v>0.7058</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>28</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.1232</v>
+        <v>0.1248</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.3649</v>
+        <v>1.3796</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>18</v>
@@ -5833,30 +4054,30 @@
         <v>33</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.1816</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.2104</v>
+        <v>1.2083</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>0.098</v>
+        <v>0.0949</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6496</v>
+        <v>0.6318</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
@@ -5865,30 +4086,30 @@
         <v>32</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.1586</v>
+        <v>0.1601</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.9878</v>
+        <v>0.9919</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>51</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.2084</v>
+        <v>0.2069</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.2985</v>
+        <v>1.2816</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>9</v>
@@ -5897,30 +4118,30 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.0803</v>
+        <v>0.0811</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.8497</v>
+        <v>0.8513</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.0876</v>
+        <v>0.0908</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.9265</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>12</v>
@@ -5929,62 +4150,62 @@
         <v>21</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.1036</v>
+        <v>0.1046</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.0509</v>
+        <v>1.0474</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.0917</v>
+        <v>0.095</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.9309</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1121</v>
+        <v>0.1178</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.2423</v>
+        <v>1.3026</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>19</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0795</v>
+        <v>0.0789</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.8813</v>
+        <v>0.8729</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>18</v>
@@ -5993,30 +4214,30 @@
         <v>31</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.1533</v>
+        <v>0.1546</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.0163</v>
+        <v>1.0292</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.1339</v>
+        <v>0.1367</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.8879</v>
+        <v>0.9097</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>6</v>
@@ -6028,10 +4249,10 @@
         <v>178</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.1524</v>
+        <v>0.1525</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9495</v>
+        <v>0.9447</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>29</v>
@@ -6043,12 +4264,12 @@
         <v>0.1355</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.844</v>
+        <v>0.8397</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>9</v>
@@ -6060,10 +4281,10 @@
         <v>178</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.0748</v>
+        <v>0.0749</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.7912</v>
+        <v>0.7856</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>24</v>
@@ -6075,12 +4296,12 @@
         <v>0.1095</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.1581</v>
+        <v>1.1494</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>12</v>
@@ -6092,10 +4313,10 @@
         <v>178</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.1164</v>
+        <v>0.1165</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.181</v>
+        <v>1.1662</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>13</v>
@@ -6104,15 +4325,15 @@
         <v>217</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.0626</v>
+        <v>0.0627</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.6349</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>15</v>
@@ -6127,7 +4348,7 @@
         <v>0.0951</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.0533</v>
+        <v>1.0514</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>18</v>
@@ -6139,12 +4360,12 @@
         <v>0.0835</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.9246</v>
+        <v>0.9229</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>18</v>
@@ -6156,10 +4377,10 @@
         <v>178</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.1207</v>
+        <v>0.1206</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.8002</v>
+        <v>0.8029</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>40</v>
@@ -6171,12 +4392,12 @@
         <v>0.182</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.207</v>
+        <v>1.2112</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>6</v>
@@ -6185,30 +4406,30 @@
         <v>37</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.1534</v>
+        <v>0.1546</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.9554</v>
+        <v>0.9579</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H57" s="4" t="n">
         <v>158</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.1469</v>
+        <v>0.1528</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0.9154</v>
+        <v>0.9464</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>9</v>
@@ -6217,94 +4438,94 @@
         <v>33</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.1338</v>
+        <v>0.1349</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.4149</v>
+        <v>1.415</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>158</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.0834</v>
+        <v>0.0892</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.8822</v>
+        <v>0.9362</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.0875</v>
+        <v>0.0922</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.888</v>
+        <v>0.9229</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" s="4" t="n">
         <v>158</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.0895</v>
+        <v>0.0839</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.9084</v>
+        <v>0.8399</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.0599</v>
+        <v>0.0564</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.6632</v>
+        <v>0.624</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>158</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.1175</v>
+        <v>0.1118</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.3017</v>
+        <v>1.2358</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>18</v>
@@ -6313,13 +4534,13 @@
         <v>50</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.2032</v>
+        <v>0.2047</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.347</v>
+        <v>1.3624</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>16</v>
@@ -6331,44 +4552,44 @@
         <v>0.1058</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.7017</v>
+        <v>0.7039</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.1332</v>
+        <v>0.1365</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.8297</v>
+        <v>0.8458</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>28</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.1402</v>
+        <v>0.1378</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.8735</v>
+        <v>0.8534</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>9</v>
@@ -6377,62 +4598,62 @@
         <v>9</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.0474</v>
+        <v>0.047</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.5009</v>
+        <v>0.493</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.0895</v>
+        <v>0.0879</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.9467</v>
+        <v>0.9228</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.0747</v>
+        <v>0.0786</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.7577</v>
+        <v>0.7865</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.1311</v>
+        <v>0.1288</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1.3302</v>
+        <v>1.2897</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>15</v>
@@ -6441,30 +4662,30 @@
         <v>27</v>
       </c>
       <c r="D65" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>1.4042</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H65" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>0.1281</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>1.4195</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>202</v>
-      </c>
       <c r="I65" s="4" t="n">
-        <v>0.0617</v>
+        <v>0.0651</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.6833</v>
+        <v>0.7196</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>18</v>
@@ -6473,30 +4694,30 @@
         <v>50</v>
       </c>
       <c r="D66" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H66" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="E66" s="4" t="n">
-        <v>0.2361</v>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>1.5655</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>202</v>
-      </c>
       <c r="I66" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.137</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.8946</v>
+        <v>0.9115</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>6</v>
@@ -6508,10 +4729,10 @@
         <v>154</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.2092</v>
+        <v>0.2093</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.3034</v>
+        <v>1.2967</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>41</v>
@@ -6523,12 +4744,12 @@
         <v>0.175</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.09</v>
+        <v>1.0843</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>9</v>
@@ -6540,10 +4761,10 @@
         <v>154</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.1265</v>
+        <v>0.1266</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.3385</v>
+        <v>1.3285</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>20</v>
@@ -6555,12 +4776,12 @@
         <v>0.0864</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.9138</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>12</v>
@@ -6572,10 +4793,10 @@
         <v>154</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.0975</v>
+        <v>0.0976</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.9895</v>
+        <v>0.9775</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>27</v>
@@ -6584,15 +4805,15 @@
         <v>233</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.1148</v>
+        <v>0.1149</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1.1646</v>
+        <v>1.1498</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>15</v>
@@ -6607,7 +4828,7 @@
         <v>0.0497</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.5503</v>
+        <v>0.5494</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>25</v>
@@ -6619,12 +4840,12 @@
         <v>0.1062</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1.1766</v>
+        <v>1.1744</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>18</v>
@@ -6639,7 +4860,7 @@
         <v>0.173</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.1472</v>
+        <v>1.1511</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>33</v>
@@ -6651,140 +4872,140 @@
         <v>0.1422</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.943</v>
+        <v>0.9463</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D72" s="4" t="n">
         <v>236</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.1888</v>
+        <v>0.1928</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.1759</v>
+        <v>1.1943</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>26</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.1341</v>
+        <v>0.1355</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.8355</v>
+        <v>0.8392</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D73" s="4" t="n">
         <v>236</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.0933</v>
+        <v>0.0973</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0.9869</v>
+        <v>1.0211</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1.0683</v>
+        <v>1.0704</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D74" s="4" t="n">
         <v>236</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.1094</v>
+        <v>0.1055</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.1105</v>
+        <v>1.0567</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.1107</v>
+        <v>0.1166</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1.1232</v>
+        <v>1.1671</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>236</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0.101</v>
+        <v>0.097</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.1186</v>
+        <v>1.0727</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.0772</v>
+        <v>0.0732</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.8553</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>18</v>
@@ -6799,19 +5020,19 @@
         <v>0.1762</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.1686</v>
+        <v>1.1727</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>29</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.1475</v>
+        <v>0.1488</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>0.9779</v>
+        <v>0.9905</v>
       </c>
     </row>
     <row r="77">
@@ -6825,25 +5046,25 @@
         <v>38</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.1726</v>
+        <v>0.172</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.0754</v>
+        <v>1.0653</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.1809</v>
+        <v>0.1825</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.1271</v>
+        <v>1.1307</v>
       </c>
     </row>
     <row r="78">
@@ -6857,25 +5078,25 @@
         <v>13</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.0618</v>
+        <v>0.0615</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.6532</v>
+        <v>0.6458</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.1362</v>
+        <v>0.1387</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.4404</v>
+        <v>1.4555</v>
       </c>
     </row>
     <row r="79">
@@ -6886,28 +5107,28 @@
         <v>12</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0.0705</v>
+        <v>0.0746</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.7158</v>
+        <v>0.7465</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.1032</v>
+        <v>0.1065</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.0473</v>
+        <v>1.0663</v>
       </c>
     </row>
     <row r="80">
@@ -6921,25 +5142,25 @@
         <v>18</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>0.0827</v>
+        <v>0.0824</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9167</v>
+        <v>0.9111</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.0969</v>
+        <v>0.1003</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>1.0737</v>
+        <v>1.1085</v>
       </c>
     </row>
     <row r="81">
@@ -6953,30 +5174,30 @@
         <v>29</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0.1337</v>
+        <v>0.1331</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.8863</v>
+        <v>0.8856</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.1467</v>
+        <v>0.1435</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.973</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>6</v>
@@ -6988,10 +5209,10 @@
         <v>162</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0.1886</v>
+        <v>0.1887</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.1748</v>
+        <v>1.1688</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>27</v>
@@ -7000,15 +5221,15 @@
         <v>230</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.1203</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.7488</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>9</v>
@@ -7023,7 +5244,7 @@
         <v>0.0872</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9218</v>
+        <v>0.9151</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>28</v>
@@ -7035,12 +5256,12 @@
         <v>0.12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1.2689</v>
+        <v>1.2593</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>12</v>
@@ -7052,10 +5273,10 @@
         <v>162</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>0.0875</v>
+        <v>0.0876</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.888</v>
+        <v>0.8773</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>29</v>
@@ -7064,15 +5285,15 @@
         <v>230</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0.1243</v>
+        <v>0.1244</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.2613</v>
+        <v>1.2453</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>15</v>
@@ -7087,7 +5308,7 @@
         <v>0.1317</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.4592</v>
+        <v>1.4565</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>18</v>
@@ -7096,15 +5317,15 @@
         <v>230</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0.079</v>
+        <v>0.0791</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0.8757</v>
+        <v>0.8741</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>18</v>
@@ -7116,10 +5337,10 @@
         <v>162</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.1147</v>
+        <v>0.1146</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.7604</v>
+        <v>0.7629</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>37</v>
@@ -7131,7 +5352,7 @@
         <v>0.1602</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1.0623</v>
+        <v>1.066</v>
       </c>
     </row>
   </sheetData>
@@ -7151,42 +5372,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -7194,23 +5415,23 @@
         <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t xml:space="preserve">date_local</t>
   </si>
@@ -86,268 +86,265 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters v cronulla-sutherland sharks</t>
+    <t xml:space="preserve">dolphins v sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_wing 1.22 (off 1.21 x def 1.01): Mark Nawaqanitawase; left_centre 1.17 (off 1.05 x def 1.12): Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_centre 1.47 (off 1.37 x def 1.07): Herbie Farnworth; fullback 1.83 (off 1.56 x def 1.18): Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers v newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No wing/centre/fullback focus &gt;= 1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_expected_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_attack_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_conceded_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_defence_conceded_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_concede_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_concede_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matchup_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_channel_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matchup_signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focus_player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focus_player_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260925-1950-dolphins-sydney-roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow (last 2026-09-12, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako (last 2026-09-12, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco (last 2026-09-19, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260927-1600-penrith-panthers-newcastle-knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga (last 2026-09-20, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards (last 2026-09-13, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner (last 2026-09-06, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins (last 2026-09-13, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">away</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_centre 1.51 (off 1.42 x def 1.07): KL Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.28 (off 1.19 x def 1.07): Mark Nawaqanitawase; right_centre 1.37 (off 1.07 x def 1.28): Billy Smith; right_wing 1.31 (off 1.17 x def 1.12): Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors v newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
     <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.28 (off 1.13 x def 1.13): Greg Marzhew; left_centre 1.29 (off 0.89 x def 1.46): Bradman Best; right_wing 1.15 (off 1.21 x def 0.96): Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_centre 1.26 (off 0.91 x def 1.38): Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_expected_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_attack_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_conceded_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_defence_conceded_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_concede_share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_concede_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matchup_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected_channel_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matchup_signal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">focus_player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">focus_player_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260919-1950-sydney-roosters-cronulla-sutherland-sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KL Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KL Iro (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neutral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy (last 2026-09-12, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Jones (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco (last 2026-09-13, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260920-1805-warriors-newcastle-knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew (last 2026-09-11, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best (last 2026-09-11, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga (last 2026-09-11, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai (last 2026-09-11, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young (last 2026-09-11, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey (last 2026-09-12, bench_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki (last 2026-09-12, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
@@ -743,9 +740,9 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="38.44" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="31.58" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.2875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.2875" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="4.14" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="8.4275" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.8575" hidden="0" customWidth="1"/>
@@ -762,7 +759,7 @@
     <col min="19" max="19" width="9.285" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="12.715" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="141.34" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="98.465" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,7 +832,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -853,49 +850,49 @@
         <v>26</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.74</v>
+        <v>1.22</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.89</v>
+        <v>1.21</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0.94</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.81</v>
+        <v>1.01</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.81</v>
+        <v>1.02</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -903,7 +900,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -921,49 +918,49 @@
         <v>28</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1.28</v>
+        <v>0.81</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.19</v>
+        <v>0.94</v>
       </c>
       <c r="I3" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L3" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="M3" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="S3" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>1.31</v>
-      </c>
       <c r="T3" s="4" t="n">
-        <v>1.17</v>
+        <v>0.9</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>29</v>
@@ -971,7 +968,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -989,49 +986,49 @@
         <v>26</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1.13</v>
+        <v>0.94</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.29</v>
+        <v>0.82</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.46</v>
+        <v>0.93</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0.95</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>1.07</v>
+        <v>0.84</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>34</v>
@@ -1039,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>30</v>
@@ -1057,52 +1054,52 @@
         <v>28</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.65</v>
+        <v>1.41</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>1.26</v>
+        <v>0.86</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>1.38</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.56</v>
+        <v>0.85</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.89</v>
+        <v>1.36</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>0.63</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1130,10 +1127,10 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="58.1625" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="38.44" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="51.3025" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="31.58" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.2875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15.2875" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="4.14" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="17.0025" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="11" hidden="0" customWidth="1"/>
@@ -1148,8 +1145,8 @@
     <col min="18" max="18" width="11.8575" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="19.575" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="20.4325" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="54.7325" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="17.0025" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="53.0175" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1160,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1175,619 +1172,619 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.2401</v>
+        <v>4.4409</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.1429</v>
+        <v>0.1513</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.8853</v>
+        <v>0.9353</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1355</v>
+        <v>0.1409</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.8392</v>
+        <v>0.8708</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.7429</v>
+        <v>0.8145</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.4984</v>
+        <v>0.5773</v>
       </c>
       <c r="T2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.2401</v>
+        <v>4.4409</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.1315</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1.415</v>
+        <v>1.3748</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.102</v>
+        <v>0.1025</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>1.0704</v>
+        <v>1.0719</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1.5146</v>
+        <v>1.4736</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.5999</v>
+        <v>0.6175</v>
       </c>
       <c r="T3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4.2401</v>
+        <v>4.4409</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0805</v>
+        <v>0.1553</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.8055</v>
+        <v>1.5581</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1166</v>
+        <v>0.1171</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1.1671</v>
+        <v>1.1752</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.9402</v>
+        <v>1.8311</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.3903</v>
+        <v>0.7994</v>
       </c>
       <c r="T4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="V4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4.2401</v>
+        <v>4.4409</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0603</v>
+        <v>0.0762</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.6672</v>
+        <v>0.8478</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0735</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.8095</v>
+        <v>0.8176</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.5401</v>
+        <v>0.6931</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.203</v>
+        <v>0.273</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="U5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.2401</v>
+        <v>4.4409</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.15</v>
+        <v>0.1349</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.8958</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>29</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1488</v>
+        <v>0.1496</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.9905</v>
+        <v>0.993</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.9889</v>
+        <v>0.8896</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6176</v>
+        <v>0.587</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.4997</v>
+        <v>4.6076</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1928</v>
+        <v>0.1952</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.1943</v>
+        <v>1.2066</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>195</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1734</v>
+        <v>0.1639</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.0741</v>
+        <v>1.0132</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.2828</v>
+        <v>1.2225</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.9182</v>
+        <v>0.9119</v>
       </c>
       <c r="T7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="V7" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.4997</v>
+        <v>4.6076</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0973</v>
+        <v>0.1005</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.0211</v>
+        <v>1.0509</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>195</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0831</v>
+        <v>0.1068</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.8715</v>
+        <v>1.1164</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.8899</v>
+        <v>1.1732</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.3761</v>
+        <v>0.5173</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="V8" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.4997</v>
+        <v>4.6076</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1055</v>
+        <v>0.1008</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.0567</v>
+        <v>1.0111</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>195</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0834</v>
+        <v>0.0929</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.835</v>
+        <v>0.9319</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8823</v>
+        <v>0.9422</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.4329</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="V9" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.4997</v>
+        <v>4.6076</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -1796,66 +1793,66 @@
         <v>23</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.097</v>
+        <v>0.0962</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.0727</v>
+        <v>1.07</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>195</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1159</v>
+        <v>0.0921</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.2811</v>
+        <v>1.0245</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.3742</v>
+        <v>1.0963</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.5511</v>
+        <v>0.4545</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.4997</v>
+        <v>4.6076</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
@@ -1864,51 +1861,51 @@
         <v>42</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1762</v>
+        <v>0.1748</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.1727</v>
+        <v>1.1607</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>195</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1678</v>
+        <v>0.1394</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.1167</v>
+        <v>0.9253</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.3095</v>
+        <v>1.0741</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.8725</v>
+        <v>0.7459</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="V11" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>31</v>
@@ -1923,7 +1920,7 @@
         <v>26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.0539</v>
+        <v>3.2087</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>6</v>
@@ -1932,51 +1929,51 @@
         <v>33</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.1807</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.1304</v>
+        <v>1.1165</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.1528</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.1307</v>
+        <v>0.9444</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.2782</v>
+        <v>1.0545</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.8347</v>
+        <v>0.5541</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="U12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>31</v>
@@ -1991,7 +1988,7 @@
         <v>26</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.0539</v>
+        <v>3.2087</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>9</v>
@@ -2000,51 +1997,51 @@
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.0847</v>
+        <v>0.0839</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8892</v>
+        <v>0.8773</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1387</v>
+        <v>0.0893</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.4555</v>
+        <v>0.9332</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.2942</v>
+        <v>0.8187</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.499</v>
+        <v>0.2543</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="U13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="V13" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>31</v>
@@ -2059,7 +2056,7 @@
         <v>26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.0539</v>
+        <v>3.2087</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>12</v>
@@ -2068,51 +2065,51 @@
         <v>17</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0954</v>
+        <v>0.0944</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.9548</v>
+        <v>0.9471</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1065</v>
+        <v>0.0839</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.0663</v>
+        <v>0.8417</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.0182</v>
+        <v>0.7972</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.4114</v>
+        <v>0.258</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>31</v>
@@ -2127,7 +2124,7 @@
         <v>26</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.0539</v>
+        <v>3.2087</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -2136,51 +2133,51 @@
         <v>11</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0638</v>
+        <v>0.0631</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7058</v>
+        <v>0.7022</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1003</v>
+        <v>0.1117</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.1085</v>
+        <v>1.2424</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.7824</v>
+        <v>0.8724</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.2863</v>
+        <v>0.2548</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="V15" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
@@ -2195,60 +2192,60 @@
         <v>26</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.0539</v>
+        <v>3.2087</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1816</v>
+        <v>0.1848</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.2083</v>
+        <v>1.227</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1435</v>
+        <v>0.1058</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.955</v>
+        <v>0.7024</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.154</v>
+        <v>0.8619</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.7015</v>
+        <v>0.4216</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="U16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V16" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>31</v>
@@ -2263,60 +2260,60 @@
         <v>28</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.222</v>
+        <v>4.6016</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.172</v>
+        <v>0.1546</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.0653</v>
+        <v>0.9558</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>31</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1423</v>
+        <v>0.1411</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.8816</v>
+        <v>0.8723</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.9391</v>
+        <v>0.8337</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.7713</v>
+        <v>0.6411</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V17" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>31</v>
@@ -2331,60 +2328,60 @@
         <v>28</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.222</v>
+        <v>4.6016</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0615</v>
+        <v>0.1349</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6458</v>
+        <v>1.4102</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.0658</v>
+        <v>0.0653</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.6902</v>
+        <v>0.6822</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.4457</v>
+        <v>0.9621</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.2162</v>
+        <v>0.4374</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="V18" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>31</v>
@@ -2399,60 +2396,60 @@
         <v>28</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.222</v>
+        <v>4.6016</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.0746</v>
+        <v>0.0922</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.7465</v>
+        <v>0.9248</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>25</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.1127</v>
+        <v>0.1117</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.1283</v>
+        <v>1.1213</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.8423</v>
+        <v>1.037</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.4281</v>
+        <v>0.4912</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>31</v>
@@ -2467,60 +2464,60 @@
         <v>28</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.222</v>
+        <v>4.6016</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0824</v>
+        <v>0.0564</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9111</v>
+        <v>0.6272</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>28</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.1237</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.3796</v>
+        <v>1.3756</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.257</v>
+        <v>0.8628</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5785</v>
+        <v>0.3687</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="U20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="V20" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>31</v>
@@ -2535,49 +2532,49 @@
         <v>28</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.222</v>
+        <v>4.6016</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1331</v>
+        <v>0.2047</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8856</v>
+        <v>1.3591</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0942</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6318</v>
+        <v>0.6251</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.5595</v>
+        <v>0.8496</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.4278</v>
+        <v>0.6083</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="V21" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2605,39 +2602,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -2652,7 +2649,7 @@
         <v>0.1448</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.8971</v>
+        <v>0.8952</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>25</v>
@@ -2661,15 +2658,15 @@
         <v>214</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.12</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.7429</v>
+        <v>0.7414</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -2684,7 +2681,7 @@
         <v>0.1179</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.2369</v>
+        <v>1.2328</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>21</v>
@@ -2693,15 +2690,15 @@
         <v>214</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.0979</v>
+        <v>0.098</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.0276</v>
+        <v>1.0242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
@@ -2716,7 +2713,7 @@
         <v>0.1093</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.0945</v>
+        <v>1.0969</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>27</v>
@@ -2728,12 +2725,12 @@
         <v>0.1243</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.2448</v>
+        <v>1.2475</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
@@ -2745,10 +2742,10 @@
         <v>209</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1031</v>
+        <v>1.1091</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>21</v>
@@ -2760,12 +2757,12 @@
         <v>0.0976</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.0791</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>18</v>
@@ -2777,10 +2774,10 @@
         <v>209</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1351</v>
+        <v>0.1352</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.8993</v>
+        <v>0.8973</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>37</v>
@@ -2792,12 +2789,12 @@
         <v>0.1713</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.1402</v>
+        <v>1.1375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -2812,7 +2809,7 @@
         <v>0.1254</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.7766</v>
+        <v>0.7749</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>38</v>
@@ -2824,12 +2821,12 @@
         <v>0.1828</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.1325</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -2844,7 +2841,7 @@
         <v>0.0743</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7792</v>
+        <v>0.7766</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>25</v>
@@ -2856,12 +2853,12 @@
         <v>0.1195</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.2537</v>
+        <v>1.2494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -2876,7 +2873,7 @@
         <v>0.1212</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.2132</v>
+        <v>1.2158</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>17</v>
@@ -2888,12 +2885,12 @@
         <v>0.0838</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8387</v>
+        <v>0.8405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>15</v>
@@ -2908,7 +2905,7 @@
         <v>0.1078</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.1922</v>
+        <v>1.1987</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>16</v>
@@ -2920,12 +2917,12 @@
         <v>0.0786</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.869</v>
+        <v>0.8736</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
@@ -2940,7 +2937,7 @@
         <v>0.1119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7446</v>
+        <v>0.7429</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>28</v>
@@ -2952,12 +2949,12 @@
         <v>0.137</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9115</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
@@ -2969,10 +2966,10 @@
         <v>180</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1356</v>
+        <v>0.1357</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8402</v>
+        <v>0.8384</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>38</v>
@@ -2984,12 +2981,12 @@
         <v>0.2081</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.2893</v>
+        <v>1.2865</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -3004,7 +3001,7 @@
         <v>0.069</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.724</v>
+        <v>0.7217</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>10</v>
@@ -3016,12 +3013,12 @@
         <v>0.0591</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6201</v>
+        <v>0.6182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -3036,7 +3033,7 @@
         <v>0.0643</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6435</v>
+        <v>0.6448</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>12</v>
@@ -3048,12 +3045,12 @@
         <v>0.0697</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6981</v>
+        <v>0.6996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>15</v>
@@ -3068,7 +3065,7 @@
         <v>0.089</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9842</v>
+        <v>0.9895</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>10</v>
@@ -3080,12 +3077,12 @@
         <v>0.0587</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6491</v>
+        <v>0.6524</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>18</v>
@@ -3100,7 +3097,7 @@
         <v>0.1245</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8286</v>
+        <v>0.8268</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>39</v>
@@ -3109,15 +3106,15 @@
         <v>179</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2123</v>
+        <v>0.2124</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.4131</v>
+        <v>1.4098</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -3126,30 +3123,30 @@
         <v>34</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1429</v>
+        <v>0.1441</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8853</v>
+        <v>0.8903</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1734</v>
+        <v>0.1787</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.0741</v>
+        <v>1.1042</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -3158,30 +3155,30 @@
         <v>33</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.1359</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.415</v>
+        <v>1.4213</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0831</v>
+        <v>0.0858</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8715</v>
+        <v>0.8969</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
@@ -3190,30 +3187,30 @@
         <v>19</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0805</v>
+        <v>0.0811</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8055</v>
+        <v>0.8136</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0834</v>
+        <v>0.0861</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.835</v>
+        <v>0.8638</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>15</v>
@@ -3222,62 +3219,62 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.0603</v>
+        <v>0.0608</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6672</v>
+        <v>0.676</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1159</v>
+        <v>0.1039</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.2811</v>
+        <v>1.1553</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.15</v>
+        <v>0.1552</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9984</v>
+        <v>1.0301</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1678</v>
+        <v>0.1686</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.1167</v>
+        <v>1.1191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
@@ -3292,7 +3289,7 @@
         <v>0.1513</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9373</v>
+        <v>0.9353</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>32</v>
@@ -3304,12 +3301,12 @@
         <v>0.1639</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.0154</v>
+        <v>1.0132</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -3324,7 +3321,7 @@
         <v>0.1315</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.3795</v>
+        <v>1.3748</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>21</v>
@@ -3336,12 +3333,12 @@
         <v>0.1068</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.1201</v>
+        <v>1.1164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
@@ -3356,7 +3353,7 @@
         <v>0.1553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.5546</v>
+        <v>1.5581</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>18</v>
@@ -3368,12 +3365,12 @@
         <v>0.0929</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9299</v>
+        <v>0.9319</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>15</v>
@@ -3385,10 +3382,10 @@
         <v>239</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0763</v>
+        <v>0.0762</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8432</v>
+        <v>0.8478</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>18</v>
@@ -3397,15 +3394,15 @@
         <v>195</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.0922</v>
+        <v>0.0921</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.0191</v>
+        <v>1.0245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>18</v>
@@ -3420,7 +3417,7 @@
         <v>0.1349</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8979</v>
+        <v>0.8958</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>27</v>
@@ -3432,12 +3429,12 @@
         <v>0.1394</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9274</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
@@ -3452,7 +3449,7 @@
         <v>0.1749</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.0836</v>
+        <v>1.0812</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>39</v>
@@ -3464,12 +3461,12 @@
         <v>0.1606</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9946</v>
+        <v>0.9924</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -3484,7 +3481,7 @@
         <v>0.1069</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.1217</v>
+        <v>1.118</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>20</v>
@@ -3496,12 +3493,12 @@
         <v>0.0831</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.872</v>
+        <v>0.8691</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>12</v>
@@ -3516,7 +3513,7 @@
         <v>0.0448</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4483</v>
+        <v>0.4492</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>24</v>
@@ -3528,12 +3525,12 @@
         <v>0.0988</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9895</v>
+        <v>0.9916</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>15</v>
@@ -3545,10 +3542,10 @@
         <v>176</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.0909</v>
+        <v>0.0908</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.0047</v>
+        <v>1.0101</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>26</v>
@@ -3557,15 +3554,15 @@
         <v>243</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.106</v>
+        <v>0.1059</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.1717</v>
+        <v>1.1782</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>18</v>
@@ -3580,7 +3577,7 @@
         <v>0.1271</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8459</v>
+        <v>0.844</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>34</v>
@@ -3592,12 +3589,12 @@
         <v>0.1406</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9354</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
@@ -3606,30 +3603,30 @@
         <v>38</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1796</v>
+        <v>0.182</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.1124</v>
+        <v>1.1249</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>0.1679</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.04</v>
+        <v>1.038</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
@@ -3638,30 +3635,30 @@
         <v>22</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1041</v>
+        <v>0.1055</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.0922</v>
+        <v>1.1032</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.0802</v>
+        <v>0.0827</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8417</v>
+        <v>0.8641</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>12</v>
@@ -3670,30 +3667,30 @@
         <v>19</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.0911</v>
+        <v>0.0924</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9125</v>
+        <v>0.9267</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1097</v>
+        <v>0.103</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.0983</v>
+        <v>1.0333</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>15</v>
@@ -3702,62 +3699,62 @@
         <v>32</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.148</v>
+        <v>0.1499</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.6364</v>
+        <v>1.6676</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.075</v>
+        <v>0.0772</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.8291</v>
+        <v>0.8585</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.1257</v>
+        <v>0.1229</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.8364</v>
+        <v>0.816</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.1573</v>
+        <v>0.1571</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.0469</v>
+        <v>1.0426</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>6</v>
@@ -3772,7 +3769,7 @@
         <v>0.1606</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.9946</v>
+        <v>0.9924</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>38</v>
@@ -3784,12 +3781,12 @@
         <v>0.1862</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1533</v>
+        <v>1.1507</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
@@ -3804,7 +3801,7 @@
         <v>0.0754</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.791</v>
+        <v>0.7884</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>21</v>
@@ -3813,15 +3810,15 @@
         <v>202</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.1033</v>
+        <v>0.1034</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.0841</v>
+        <v>1.0805</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>12</v>
@@ -3836,7 +3833,7 @@
         <v>0.1529</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.5306</v>
+        <v>1.534</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>16</v>
@@ -3848,12 +3845,12 @@
         <v>0.0807</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.8082</v>
+        <v>0.8099</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>15</v>
@@ -3865,10 +3862,10 @@
         <v>243</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.0557</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.6168</v>
+        <v>0.62</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>18</v>
@@ -3880,12 +3877,12 @@
         <v>0.0892</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.9864</v>
+        <v>0.9916</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>18</v>
@@ -3900,7 +3897,7 @@
         <v>0.1406</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.9354</v>
+        <v>0.9333</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>37</v>
@@ -3912,7 +3909,7 @@
         <v>0.1808</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.203</v>
+        <v>1.2002</v>
       </c>
     </row>
     <row r="42">
@@ -3926,25 +3923,25 @@
         <v>33</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.1807</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.1304</v>
+        <v>1.1165</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>31</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.1423</v>
+        <v>0.1411</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.8816</v>
+        <v>0.8723</v>
       </c>
     </row>
     <row r="43">
@@ -3958,25 +3955,25 @@
         <v>15</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.0847</v>
+        <v>0.0839</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.8892</v>
+        <v>0.8773</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.0658</v>
+        <v>0.0653</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.6902</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="44">
@@ -3990,25 +3987,25 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.0954</v>
+        <v>0.0944</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.9548</v>
+        <v>0.9471</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>25</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.1127</v>
+        <v>0.1117</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.1283</v>
+        <v>1.1213</v>
       </c>
     </row>
     <row r="45">
@@ -4022,25 +4019,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.0638</v>
+        <v>0.0631</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.7058</v>
+        <v>0.7022</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>28</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.1237</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.3796</v>
+        <v>1.3756</v>
       </c>
     </row>
     <row r="46">
@@ -4051,33 +4048,33 @@
         <v>18</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.1816</v>
+        <v>0.1848</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.2083</v>
+        <v>1.227</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0942</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6318</v>
+        <v>0.6251</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
@@ -4086,30 +4083,30 @@
         <v>32</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.1601</v>
+        <v>0.1624</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.9919</v>
+        <v>1.0036</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.2069</v>
+        <v>0.2062</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.2816</v>
+        <v>1.2746</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>9</v>
@@ -4118,30 +4115,30 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.0811</v>
+        <v>0.0823</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.8513</v>
+        <v>0.8605</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>22</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.0908</v>
+        <v>0.0923</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.953</v>
+        <v>0.9648</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>12</v>
@@ -4150,62 +4147,62 @@
         <v>21</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.1046</v>
+        <v>0.1061</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.0474</v>
+        <v>1.0644</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>23</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.095</v>
+        <v>0.0964</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.9508</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.11</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.3026</v>
+        <v>1.2238</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>19</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0789</v>
+        <v>0.0802</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.8729</v>
+        <v>0.8914</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>18</v>
@@ -4214,30 +4211,30 @@
         <v>31</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.1546</v>
+        <v>0.1569</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.0292</v>
+        <v>1.0413</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>33</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.1367</v>
+        <v>0.1389</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.9097</v>
+        <v>0.9219</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>6</v>
@@ -4252,7 +4249,7 @@
         <v>0.1525</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9447</v>
+        <v>0.9427</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>29</v>
@@ -4261,15 +4258,15 @@
         <v>217</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.1355</v>
+        <v>0.1356</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.8397</v>
+        <v>0.8379</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>9</v>
@@ -4284,7 +4281,7 @@
         <v>0.0749</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.7856</v>
+        <v>0.7831</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>24</v>
@@ -4293,15 +4290,15 @@
         <v>217</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.1095</v>
+        <v>0.1096</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.1494</v>
+        <v>1.1456</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>12</v>
@@ -4316,7 +4313,7 @@
         <v>0.1165</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.1662</v>
+        <v>1.1687</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>13</v>
@@ -4325,15 +4322,15 @@
         <v>217</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.0627</v>
+        <v>0.0626</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.6272</v>
+        <v>0.6285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>15</v>
@@ -4345,10 +4342,10 @@
         <v>178</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.0951</v>
+        <v>0.095</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.0514</v>
+        <v>1.057</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>18</v>
@@ -4357,15 +4354,15 @@
         <v>217</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.0835</v>
+        <v>0.0834</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.9229</v>
+        <v>0.9278</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>18</v>
@@ -4377,10 +4374,10 @@
         <v>178</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.1206</v>
+        <v>0.1207</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.8029</v>
+        <v>0.8011</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>40</v>
@@ -4392,12 +4389,12 @@
         <v>0.182</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.2112</v>
+        <v>1.2084</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>6</v>
@@ -4412,7 +4409,7 @@
         <v>0.1546</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.9579</v>
+        <v>0.9558</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>24</v>
@@ -4424,12 +4421,12 @@
         <v>0.1528</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0.9464</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>9</v>
@@ -4444,7 +4441,7 @@
         <v>0.1349</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.415</v>
+        <v>1.4102</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>14</v>
@@ -4453,15 +4450,15 @@
         <v>158</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.0892</v>
+        <v>0.0893</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.9362</v>
+        <v>0.9332</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>12</v>
@@ -4476,7 +4473,7 @@
         <v>0.0922</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.9229</v>
+        <v>0.9248</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>13</v>
@@ -4488,12 +4485,12 @@
         <v>0.0839</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.8399</v>
+        <v>0.8417</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>15</v>
@@ -4508,7 +4505,7 @@
         <v>0.0564</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.624</v>
+        <v>0.6272</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>18</v>
@@ -4517,15 +4514,15 @@
         <v>158</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.2358</v>
+        <v>1.2424</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>18</v>
@@ -4540,7 +4537,7 @@
         <v>0.2047</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.3624</v>
+        <v>1.3591</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>16</v>
@@ -4552,12 +4549,12 @@
         <v>0.1058</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.7039</v>
+        <v>0.7024</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>6</v>
@@ -4569,10 +4566,10 @@
         <v>208</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.1365</v>
+        <v>0.1366</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.8458</v>
+        <v>0.844</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>28</v>
@@ -4584,12 +4581,12 @@
         <v>0.1378</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.8534</v>
+        <v>0.8516</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>9</v>
@@ -4604,7 +4601,7 @@
         <v>0.047</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.493</v>
+        <v>0.4915</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>18</v>
@@ -4613,15 +4610,15 @@
         <v>206</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.0879</v>
+        <v>0.088</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.9228</v>
+        <v>0.9198</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>12</v>
@@ -4633,10 +4630,10 @@
         <v>208</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.0786</v>
+        <v>0.0785</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.7865</v>
+        <v>0.7882</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>27</v>
@@ -4648,12 +4645,12 @@
         <v>0.1288</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1.2897</v>
+        <v>1.2925</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>15</v>
@@ -4668,7 +4665,7 @@
         <v>0.127</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.4042</v>
+        <v>1.4119</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>13</v>
@@ -4677,15 +4674,15 @@
         <v>206</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0.0651</v>
+        <v>0.065</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.7196</v>
+        <v>0.7233</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>18</v>
@@ -4697,10 +4694,10 @@
         <v>208</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.557</v>
+        <v>1.5533</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>28</v>
@@ -4712,12 +4709,12 @@
         <v>0.137</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.9115</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>6</v>
@@ -4732,7 +4729,7 @@
         <v>0.2093</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.2967</v>
+        <v>1.2939</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>41</v>
@@ -4741,15 +4738,15 @@
         <v>233</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0.175</v>
+        <v>0.1751</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.0843</v>
+        <v>1.0819</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>9</v>
@@ -4764,7 +4761,7 @@
         <v>0.1266</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.3285</v>
+        <v>1.3241</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>20</v>
@@ -4773,15 +4770,15 @@
         <v>233</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.0864</v>
+        <v>0.0865</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.907</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>12</v>
@@ -4796,7 +4793,7 @@
         <v>0.0976</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.9775</v>
+        <v>0.9795</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>27</v>
@@ -4805,15 +4802,15 @@
         <v>233</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.1149</v>
+        <v>0.1148</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1.1498</v>
+        <v>1.1523</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>15</v>
@@ -4825,10 +4822,10 @@
         <v>154</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.0497</v>
+        <v>0.0496</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.5494</v>
+        <v>0.552</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>25</v>
@@ -4840,12 +4837,12 @@
         <v>0.1062</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1.1744</v>
+        <v>1.1808</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>18</v>
@@ -4860,7 +4857,7 @@
         <v>0.173</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.1511</v>
+        <v>1.1485</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>33</v>
@@ -4872,108 +4869,108 @@
         <v>0.1422</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.9463</v>
+        <v>0.9441</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.1928</v>
+        <v>0.1952</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.1943</v>
+        <v>1.2066</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.1355</v>
+        <v>0.1409</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.8392</v>
+        <v>0.8708</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.0973</v>
+        <v>0.1005</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1.0211</v>
+        <v>1.0509</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.102</v>
+        <v>0.1025</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1.0704</v>
+        <v>1.0719</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.1055</v>
+        <v>0.1008</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.0567</v>
+        <v>1.0111</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>23</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.1166</v>
+        <v>0.1171</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1.1671</v>
+        <v>1.1752</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>15</v>
@@ -4982,30 +4979,30 @@
         <v>23</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0.097</v>
+        <v>0.0962</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.0727</v>
+        <v>1.07</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0735</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.8095</v>
+        <v>0.8176</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>18</v>
@@ -5014,30 +5011,30 @@
         <v>42</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.1762</v>
+        <v>0.1748</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.1727</v>
+        <v>1.1607</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>29</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.1488</v>
+        <v>0.1496</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>0.9905</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>6</v>
@@ -5046,30 +5043,30 @@
         <v>38</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.172</v>
+        <v>0.1705</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.0653</v>
+        <v>1.054</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>31</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.1806</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.1307</v>
+        <v>1.1161</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>9</v>
@@ -5078,30 +5075,30 @@
         <v>13</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.0615</v>
+        <v>0.0611</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.6458</v>
+        <v>0.6383</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.1387</v>
+        <v>0.1373</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.4555</v>
+        <v>1.4351</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>12</v>
@@ -5110,30 +5107,30 @@
         <v>16</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0.0746</v>
+        <v>0.0739</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.7465</v>
+        <v>0.7418</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.1065</v>
+        <v>0.1053</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.0663</v>
+        <v>1.0571</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>15</v>
@@ -5142,30 +5139,30 @@
         <v>18</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>0.0824</v>
+        <v>0.0817</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9111</v>
+        <v>0.9083</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>17</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.1003</v>
+        <v>0.0991</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>1.1085</v>
+        <v>1.1025</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>18</v>
@@ -5174,30 +5171,30 @@
         <v>29</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0.1331</v>
+        <v>0.132</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.8856</v>
+        <v>0.8762</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.1435</v>
+        <v>0.1474</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.955</v>
+        <v>0.9783</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>6</v>
@@ -5212,7 +5209,7 @@
         <v>0.1887</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.1688</v>
+        <v>1.1663</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>27</v>
@@ -5224,12 +5221,12 @@
         <v>0.1203</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.745</v>
+        <v>0.7434</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>9</v>
@@ -5244,7 +5241,7 @@
         <v>0.0872</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9151</v>
+        <v>0.9122</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>28</v>
@@ -5256,12 +5253,12 @@
         <v>0.12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1.2593</v>
+        <v>1.2551</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>12</v>
@@ -5276,7 +5273,7 @@
         <v>0.0876</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.8773</v>
+        <v>0.8791</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>29</v>
@@ -5288,12 +5285,12 @@
         <v>0.1244</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.2453</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>15</v>
@@ -5308,7 +5305,7 @@
         <v>0.1317</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.4565</v>
+        <v>1.4644</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>18</v>
@@ -5317,15 +5314,15 @@
         <v>230</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0.0791</v>
+        <v>0.079</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0.8741</v>
+        <v>0.8788</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>18</v>
@@ -5337,10 +5334,10 @@
         <v>162</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.1146</v>
+        <v>0.1147</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.7629</v>
+        <v>0.7612</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>37</v>
@@ -5352,7 +5349,7 @@
         <v>0.1602</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1.066</v>
+        <v>1.0636</v>
       </c>
     </row>
   </sheetData>
@@ -5372,42 +5369,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -5415,23 +5412,23 @@
         <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">date_local</t>
   </si>
@@ -83,259 +83,187 @@
     <t xml:space="preserve">focus_players</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins v sydney roosters</t>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters v newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right_wing 1.26 (off 1.23 x def 1.03): Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fullback 1.15 (off 1.02 x def 1.12): James Tedesco; right_centre 1.49 (off 1.08 x def 1.37): Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_expected_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_attack_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_conceded_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_defence_conceded_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_concede_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defence_concede_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matchup_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_channel_tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matchup_signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focus_player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focus_player_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20261004-1930-sydney-roosters-newcastle-knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga (last 2026-09-20, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young (last 2026-09-20, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco (last 2026-09-19, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou (last 2026-09-19, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">away</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.22 (off 1.21 x def 1.01): Mark Nawaqanitawase; left_centre 1.17 (off 1.05 x def 1.12): Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_centre 1.47 (off 1.37 x def 1.07): Herbie Farnworth; fullback 1.83 (off 1.56 x def 1.18): Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers v newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
     <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No wing/centre/fullback focus &gt;= 1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_expected_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_attack_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_conceded_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_defence_conceded_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_concede_share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defence_concede_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matchup_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected_channel_tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matchup_signal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">focus_player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">focus_player_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260925-1950-dolphins-sydney-roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neutral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow (last 2026-09-12, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako (last 2026-09-12, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-09-19, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia (last 2026-09-19, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco (last 2026-09-19, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith (last 2026-09-19, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou (last 2026-09-19, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260927-1600-penrith-panthers-newcastle-knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew (last 2026-09-20, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best (last 2026-09-20, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga (last 2026-09-20, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai (last 2026-09-20, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young (last 2026-09-20, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards (last 2026-09-13, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner (last 2026-09-06, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins (last 2026-09-13, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
@@ -740,7 +668,7 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="31.58" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30.7225" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="15.2875" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="15.2875" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="4.14" hidden="0" customWidth="1"/>
@@ -759,7 +687,7 @@
     <col min="19" max="19" width="9.285" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="12.715" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="98.465" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="89.89" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -850,49 +778,49 @@
         <v>26</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>1.17</v>
+        <v>0.98</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>1.12</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.94</v>
+        <v>1.07</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>1.1</v>
+        <v>0.56</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -900,7 +828,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -918,192 +846,56 @@
         <v>28</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.81</v>
+        <v>1.06</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.94</v>
+        <v>1.22</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>0.87</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.47</v>
+        <v>0.73</v>
       </c>
       <c r="K3" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="L3" s="4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0.82</v>
-      </c>
       <c r="S3" s="4" t="n">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.99</v>
+        <v>0.62</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:S5">
+  <conditionalFormatting sqref="G2:S3">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1127,8 +919,8 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="51.3025" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="31.58" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="50.445" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="30.7225" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="15.2875" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="15.2875" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="4.14" hidden="0" customWidth="1"/>
@@ -1146,7 +938,7 @@
     <col min="19" max="19" width="19.575" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="17.0025" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="53.0175" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="51.3025" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1157,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1172,415 +964,415 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.4409</v>
+        <v>3.7336</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.1513</v>
+        <v>0.1807</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.9353</v>
+        <v>1.1136</v>
       </c>
       <c r="N2" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1409</v>
+        <v>0.1465</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.8708</v>
+        <v>0.903</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.8145</v>
+        <v>1.0056</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.5773</v>
+        <v>0.5972</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.4409</v>
+        <v>3.7336</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.1315</v>
+        <v>0.0839</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1.3748</v>
+        <v>0.8784</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.1025</v>
+        <v>0.1066</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>1.0719</v>
+        <v>1.1158</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1.4736</v>
+        <v>0.9802</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.6175</v>
+        <v>0.3427</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4.4409</v>
+        <v>3.7336</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.1553</v>
+        <v>0.0944</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1.5581</v>
+        <v>0.9482</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1171</v>
+        <v>0.1118</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1.1752</v>
+        <v>1.1236</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.8311</v>
+        <v>1.0654</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.7994</v>
+        <v>0.3881</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4.4409</v>
+        <v>3.7336</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.0632</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.8478</v>
+        <v>0.7013</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.0735</v>
+        <v>0.0715</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.8176</v>
+        <v>0.7939</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.6931</v>
+        <v>0.5568</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.273</v>
+        <v>0.1835</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.4409</v>
+        <v>3.7336</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.1848</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.8958</v>
+        <v>1.2261</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>29</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.1555</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.993</v>
+        <v>1.0316</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.8896</v>
+        <v>1.2648</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.587</v>
+        <v>0.6979</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.6076</v>
+        <v>5.1887</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
@@ -1589,66 +1381,66 @@
         <v>47</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1952</v>
+        <v>0.1976</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.2066</v>
+        <v>1.2178</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1639</v>
+        <v>0.1412</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.0132</v>
+        <v>0.87</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.2225</v>
+        <v>1.0595</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.9119</v>
+        <v>0.9118</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.6076</v>
+        <v>5.1887</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
@@ -1657,66 +1449,66 @@
         <v>24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1005</v>
+        <v>0.1017</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.0509</v>
+        <v>1.0648</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1068</v>
+        <v>0.0652</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.1164</v>
+        <v>0.6831</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.1732</v>
+        <v>0.7274</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.5173</v>
+        <v>0.3685</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.6076</v>
+        <v>5.1887</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -1725,66 +1517,66 @@
         <v>24</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.102</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.0111</v>
+        <v>1.0243</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0929</v>
+        <v>0.1117</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.9319</v>
+        <v>1.1225</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.9422</v>
+        <v>1.1498</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.4329</v>
+        <v>0.6071</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.6076</v>
+        <v>5.1887</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -1793,788 +1585,108 @@
         <v>23</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0962</v>
+        <v>0.0974</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.07</v>
+        <v>1.0814</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0921</v>
+        <v>0.1237</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.0245</v>
+        <v>1.3737</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.0963</v>
+        <v>1.4855</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.7095</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.6076</v>
+        <v>5.1887</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1748</v>
+        <v>0.173</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.1607</v>
+        <v>1.1473</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1394</v>
+        <v>0.0942</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.9253</v>
+        <v>0.6247</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.0741</v>
+        <v>0.7167</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7459</v>
+        <v>0.5731</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>3.2087</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.1807</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>1.1165</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0.1528</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0.9444</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>1.0545</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0.5541</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>3.2087</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.0839</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.8773</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0.0893</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0.9332</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0.8187</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0.2543</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>3.2087</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0944</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.9471</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>0.0839</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0.8417</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>0.7972</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>3.2087</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.0631</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0.7022</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>0.1117</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>1.2424</v>
-      </c>
-      <c r="R15" s="4" t="n">
-        <v>0.8724</v>
-      </c>
-      <c r="S15" s="4" t="n">
-        <v>0.2548</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>3.2087</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.1848</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>1.227</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>0.1058</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>0.7024</v>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>0.8619</v>
-      </c>
-      <c r="S16" s="4" t="n">
-        <v>0.4216</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>4.6016</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.1546</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>0.9558</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>0.1411</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0.8723</v>
-      </c>
-      <c r="R17" s="4" t="n">
-        <v>0.8337</v>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>0.6411</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>4.6016</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.1349</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>1.4102</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>0.0653</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>0.6822</v>
-      </c>
-      <c r="R18" s="4" t="n">
-        <v>0.9621</v>
-      </c>
-      <c r="S18" s="4" t="n">
-        <v>0.4374</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>4.6016</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0.9248</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>0.1117</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>1.1213</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="S19" s="4" t="n">
-        <v>0.4912</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>4.6016</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0.0564</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0.6272</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0.1237</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>1.3756</v>
-      </c>
-      <c r="R20" s="4" t="n">
-        <v>0.8628</v>
-      </c>
-      <c r="S20" s="4" t="n">
-        <v>0.3687</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>4.6016</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.2047</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>1.3591</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0.0942</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0.6251</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>0.8496</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>0.6083</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2602,39 +1714,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -2646,10 +1758,10 @@
         <v>209</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1448</v>
+        <v>0.1449</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.8952</v>
+        <v>0.8929</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>25</v>
@@ -2661,12 +1773,12 @@
         <v>0.12</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.7414</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -2681,7 +1793,7 @@
         <v>0.1179</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.2328</v>
+        <v>1.2344</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>21</v>
@@ -2690,15 +1802,15 @@
         <v>214</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.098</v>
+        <v>0.0979</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.0242</v>
+        <v>1.0255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
@@ -2713,7 +1825,7 @@
         <v>0.1093</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.0969</v>
+        <v>1.0981</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>27</v>
@@ -2725,12 +1837,12 @@
         <v>0.1243</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.2475</v>
+        <v>1.2489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
@@ -2745,7 +1857,7 @@
         <v>0.0997</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1091</v>
+        <v>1.1076</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>21</v>
@@ -2757,12 +1869,12 @@
         <v>0.0976</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.085</v>
+        <v>1.0835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>18</v>
@@ -2777,7 +1889,7 @@
         <v>0.1352</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.8973</v>
+        <v>0.8966</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>37</v>
@@ -2786,15 +1898,15 @@
         <v>214</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1713</v>
+        <v>0.1714</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.1375</v>
+        <v>1.1367</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -2809,7 +1921,7 @@
         <v>0.1254</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.7749</v>
+        <v>0.7729</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>38</v>
@@ -2818,15 +1930,15 @@
         <v>206</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1828</v>
+        <v>0.1829</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.13</v>
+        <v>1.127</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -2841,7 +1953,7 @@
         <v>0.0743</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7766</v>
+        <v>0.7776</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>25</v>
@@ -2853,12 +1965,12 @@
         <v>0.1195</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.2494</v>
+        <v>1.2511</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -2873,7 +1985,7 @@
         <v>0.1212</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.2158</v>
+        <v>1.2172</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>17</v>
@@ -2885,12 +1997,12 @@
         <v>0.0838</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8405</v>
+        <v>0.8414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>15</v>
@@ -2905,7 +2017,7 @@
         <v>0.1078</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.1987</v>
+        <v>1.1972</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>16</v>
@@ -2917,12 +2029,12 @@
         <v>0.0786</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8736</v>
+        <v>0.8725</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
@@ -2937,7 +2049,7 @@
         <v>0.1119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7429</v>
+        <v>0.7424</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>28</v>
@@ -2949,12 +2061,12 @@
         <v>0.137</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9094</v>
+        <v>0.9087</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
@@ -2969,7 +2081,7 @@
         <v>0.1357</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8384</v>
+        <v>0.8363</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>38</v>
@@ -2978,15 +2090,15 @@
         <v>179</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2081</v>
+        <v>0.2082</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.2865</v>
+        <v>1.2831</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -3001,7 +2113,7 @@
         <v>0.069</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7217</v>
+        <v>0.7226</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>10</v>
@@ -3013,12 +2125,12 @@
         <v>0.0591</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6182</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -3030,10 +2142,10 @@
         <v>180</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.0643</v>
+        <v>0.0642</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6448</v>
+        <v>0.6455</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>12</v>
@@ -3045,12 +2157,12 @@
         <v>0.0697</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6996</v>
+        <v>0.7003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>15</v>
@@ -3065,7 +2177,7 @@
         <v>0.089</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9895</v>
+        <v>0.9882</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>10</v>
@@ -3077,12 +2189,12 @@
         <v>0.0587</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6524</v>
+        <v>0.6516</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>18</v>
@@ -3094,10 +2206,10 @@
         <v>180</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1245</v>
+        <v>0.1246</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8268</v>
+        <v>0.8262</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>39</v>
@@ -3109,12 +2221,12 @@
         <v>0.2124</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.4098</v>
+        <v>1.4088</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -3123,30 +2235,30 @@
         <v>34</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1441</v>
+        <v>0.1446</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8903</v>
+        <v>0.8915</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1787</v>
+        <v>0.1773</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.1042</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -3155,30 +2267,30 @@
         <v>33</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1359</v>
+        <v>0.1365</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.4213</v>
+        <v>1.4289</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0858</v>
+        <v>0.078</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8969</v>
+        <v>0.8163</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
@@ -3187,30 +2299,30 @@
         <v>19</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0811</v>
+        <v>0.0814</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8136</v>
+        <v>0.8177</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0861</v>
+        <v>0.0877</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8638</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>15</v>
@@ -3219,62 +2331,62 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.0608</v>
+        <v>0.061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.676</v>
+        <v>0.6778</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1039</v>
+        <v>0.1059</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.1553</v>
+        <v>1.1755</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1552</v>
+        <v>0.1518</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.0301</v>
+        <v>1.0072</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>34</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1686</v>
+        <v>0.1718</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.1191</v>
+        <v>1.1393</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
@@ -3286,10 +2398,10 @@
         <v>239</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1513</v>
+        <v>0.1514</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9353</v>
+        <v>0.9328</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>32</v>
@@ -3298,15 +2410,15 @@
         <v>195</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1639</v>
+        <v>0.164</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.0132</v>
+        <v>1.0105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -3321,7 +2433,7 @@
         <v>0.1315</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.3748</v>
+        <v>1.3766</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>21</v>
@@ -3333,12 +2445,12 @@
         <v>0.1068</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.1164</v>
+        <v>1.1179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
@@ -3353,7 +2465,7 @@
         <v>0.1553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.5581</v>
+        <v>1.5598</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>18</v>
@@ -3365,12 +2477,12 @@
         <v>0.0929</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9319</v>
+        <v>0.9329</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>15</v>
@@ -3385,7 +2497,7 @@
         <v>0.0762</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8478</v>
+        <v>0.8467</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>18</v>
@@ -3397,12 +2509,12 @@
         <v>0.0921</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.0245</v>
+        <v>1.0232</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>18</v>
@@ -3417,7 +2529,7 @@
         <v>0.1349</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8958</v>
+        <v>0.8952</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>27</v>
@@ -3429,12 +2541,12 @@
         <v>0.1394</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9253</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
@@ -3446,10 +2558,10 @@
         <v>176</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1749</v>
+        <v>0.175</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.0812</v>
+        <v>1.0784</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>39</v>
@@ -3461,12 +2573,12 @@
         <v>0.1606</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9924</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -3481,7 +2593,7 @@
         <v>0.1069</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.118</v>
+        <v>1.1194</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>20</v>
@@ -3493,12 +2605,12 @@
         <v>0.0831</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8691</v>
+        <v>0.8703</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>12</v>
@@ -3513,7 +2625,7 @@
         <v>0.0448</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4492</v>
+        <v>0.4496</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>24</v>
@@ -3525,12 +2637,12 @@
         <v>0.0988</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9916</v>
+        <v>0.9927</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>15</v>
@@ -3545,7 +2657,7 @@
         <v>0.0908</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.0101</v>
+        <v>1.0088</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>26</v>
@@ -3557,12 +2669,12 @@
         <v>0.1059</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.1782</v>
+        <v>1.1766</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>18</v>
@@ -3577,7 +2689,7 @@
         <v>0.1271</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.844</v>
+        <v>0.8434</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>34</v>
@@ -3589,12 +2701,12 @@
         <v>0.1406</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9333</v>
+        <v>0.9326</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
@@ -3609,7 +2721,7 @@
         <v>0.182</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.1249</v>
+        <v>1.122</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>31</v>
@@ -3618,15 +2730,15 @@
         <v>184</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1679</v>
+        <v>0.168</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.038</v>
+        <v>1.0353</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
@@ -3641,7 +2753,7 @@
         <v>0.1055</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.1032</v>
+        <v>1.1047</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>15</v>
@@ -3650,15 +2762,15 @@
         <v>184</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.0827</v>
+        <v>0.0826</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8641</v>
+        <v>0.8652</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>12</v>
@@ -3670,10 +2782,10 @@
         <v>207</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.0924</v>
+        <v>0.0923</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9267</v>
+        <v>0.9277</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>19</v>
@@ -3685,12 +2797,12 @@
         <v>0.103</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.0333</v>
+        <v>1.0344</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>15</v>
@@ -3702,10 +2814,10 @@
         <v>207</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1499</v>
+        <v>0.15</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.6676</v>
+        <v>1.6654</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>14</v>
@@ -3717,12 +2829,12 @@
         <v>0.0772</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.8585</v>
+        <v>0.8574</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>18</v>
@@ -3737,7 +2849,7 @@
         <v>0.1229</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.816</v>
+        <v>0.8154</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>29</v>
@@ -3749,12 +2861,12 @@
         <v>0.1571</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.0426</v>
+        <v>1.0419</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>6</v>
@@ -3763,30 +2875,30 @@
         <v>39</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.1606</v>
+        <v>0.1657</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.9924</v>
+        <v>1.0214</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>38</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.1862</v>
+        <v>0.1888</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1507</v>
+        <v>1.1637</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
@@ -3795,94 +2907,94 @@
         <v>18</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.0754</v>
+        <v>0.0778</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7884</v>
+        <v>0.8146</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.1034</v>
+        <v>0.1048</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.0805</v>
+        <v>1.0971</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.1529</v>
+        <v>0.1498</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.534</v>
+        <v>1.5046</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.0807</v>
+        <v>0.0818</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.8099</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0557</v>
+        <v>0.0535</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.62</v>
+        <v>0.5947</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.0892</v>
+        <v>0.0904</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.9916</v>
+        <v>1.0042</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>18</v>
@@ -3891,30 +3003,30 @@
         <v>34</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.1406</v>
+        <v>0.1451</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.9333</v>
+        <v>0.9623</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0.1808</v>
+        <v>0.1787</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.2002</v>
+        <v>1.1852</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>6</v>
@@ -3929,7 +3041,7 @@
         <v>0.1807</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.1165</v>
+        <v>1.1136</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>31</v>
@@ -3938,15 +3050,15 @@
         <v>222</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.1411</v>
+        <v>0.1412</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.8723</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>9</v>
@@ -3961,7 +3073,7 @@
         <v>0.0839</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.8773</v>
+        <v>0.8784</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>14</v>
@@ -3970,15 +3082,15 @@
         <v>222</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.0653</v>
+        <v>0.0652</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.6822</v>
+        <v>0.6831</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>12</v>
@@ -3993,7 +3105,7 @@
         <v>0.0944</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.9471</v>
+        <v>0.9482</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>25</v>
@@ -4005,12 +3117,12 @@
         <v>0.1117</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.1213</v>
+        <v>1.1225</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>15</v>
@@ -4022,10 +3134,10 @@
         <v>181</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.0631</v>
+        <v>0.0632</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.7022</v>
+        <v>0.7013</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>28</v>
@@ -4037,12 +3149,12 @@
         <v>0.1237</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.3756</v>
+        <v>1.3737</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>18</v>
@@ -4057,7 +3169,7 @@
         <v>0.1848</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.227</v>
+        <v>1.2261</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>20</v>
@@ -4069,12 +3181,12 @@
         <v>0.0942</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6251</v>
+        <v>0.6247</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
@@ -4089,7 +3201,7 @@
         <v>0.1624</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.0036</v>
+        <v>1.001</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>50</v>
@@ -4098,15 +3210,15 @@
         <v>239</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.2062</v>
+        <v>0.2063</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.2746</v>
+        <v>1.2712</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>9</v>
@@ -4121,7 +3233,7 @@
         <v>0.0823</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.8605</v>
+        <v>0.8616</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>22</v>
@@ -4133,12 +3245,12 @@
         <v>0.0923</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.9648</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>12</v>
@@ -4153,7 +3265,7 @@
         <v>0.1061</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.0644</v>
+        <v>1.0656</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>23</v>
@@ -4165,12 +3277,12 @@
         <v>0.0964</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.9678</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>15</v>
@@ -4182,10 +3294,10 @@
         <v>197</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.11</v>
+        <v>0.1101</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.2238</v>
+        <v>1.2222</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>19</v>
@@ -4197,12 +3309,12 @@
         <v>0.0802</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.8914</v>
+        <v>0.8902</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>18</v>
@@ -4217,7 +3329,7 @@
         <v>0.1569</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.0413</v>
+        <v>1.0406</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>33</v>
@@ -4229,12 +3341,12 @@
         <v>0.1389</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.9219</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>6</v>
@@ -4246,10 +3358,10 @@
         <v>178</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.1526</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9427</v>
+        <v>0.9402</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>29</v>
@@ -4261,12 +3373,12 @@
         <v>0.1356</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.8379</v>
+        <v>0.8358</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>9</v>
@@ -4281,7 +3393,7 @@
         <v>0.0749</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.7831</v>
+        <v>0.7841</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>24</v>
@@ -4293,12 +3405,12 @@
         <v>0.1096</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.1456</v>
+        <v>1.1471</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>12</v>
@@ -4313,7 +3425,7 @@
         <v>0.1165</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.1687</v>
+        <v>1.17</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>13</v>
@@ -4325,12 +3437,12 @@
         <v>0.0626</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.6285</v>
+        <v>0.6292</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>15</v>
@@ -4342,10 +3454,10 @@
         <v>178</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.095</v>
+        <v>0.0951</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.057</v>
+        <v>1.0556</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>18</v>
@@ -4357,12 +3469,12 @@
         <v>0.0834</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.9278</v>
+        <v>0.9266</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>18</v>
@@ -4377,7 +3489,7 @@
         <v>0.1207</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.8011</v>
+        <v>0.8005</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>40</v>
@@ -4389,76 +3501,76 @@
         <v>0.182</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.2084</v>
+        <v>1.2075</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.1546</v>
+        <v>0.1532</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.9558</v>
+        <v>0.9439</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.1528</v>
+        <v>0.1537</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0.9444</v>
+        <v>0.9475</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.1291</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.4102</v>
+        <v>1.3515</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.0893</v>
+        <v>0.0898</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.9332</v>
+        <v>0.9398</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>12</v>
@@ -4467,30 +3579,30 @@
         <v>22</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.0922</v>
+        <v>0.0936</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.9248</v>
+        <v>0.9405</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.0839</v>
+        <v>0.0844</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.8417</v>
+        <v>0.8474</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>15</v>
@@ -4499,30 +3611,30 @@
         <v>13</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.0564</v>
+        <v>0.0573</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.6272</v>
+        <v>0.6364</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.1117</v>
+        <v>0.1124</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.2424</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>18</v>
@@ -4531,30 +3643,30 @@
         <v>50</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.2047</v>
+        <v>0.208</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.3591</v>
+        <v>1.3797</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0.1058</v>
+        <v>0.1006</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.7024</v>
+        <v>0.6677</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>6</v>
@@ -4569,7 +3681,7 @@
         <v>0.1366</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.844</v>
+        <v>0.8418</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>28</v>
@@ -4581,12 +3693,12 @@
         <v>0.1378</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.8516</v>
+        <v>0.8494</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>9</v>
@@ -4601,7 +3713,7 @@
         <v>0.047</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.4915</v>
+        <v>0.4921</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>18</v>
@@ -4613,12 +3725,12 @@
         <v>0.088</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.9198</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>12</v>
@@ -4633,7 +3745,7 @@
         <v>0.0785</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.7882</v>
+        <v>0.789</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>27</v>
@@ -4645,12 +3757,12 @@
         <v>0.1288</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1.2925</v>
+        <v>1.2939</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>15</v>
@@ -4665,7 +3777,7 @@
         <v>0.127</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.4119</v>
+        <v>1.41</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>13</v>
@@ -4677,12 +3789,12 @@
         <v>0.065</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.7233</v>
+        <v>0.7224</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>18</v>
@@ -4697,7 +3809,7 @@
         <v>0.234</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.5533</v>
+        <v>1.5521</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>28</v>
@@ -4709,12 +3821,12 @@
         <v>0.137</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.9094</v>
+        <v>0.9087</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>6</v>
@@ -4726,10 +3838,10 @@
         <v>154</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.2093</v>
+        <v>0.2094</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.2939</v>
+        <v>1.2905</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>41</v>
@@ -4741,12 +3853,12 @@
         <v>0.1751</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.0819</v>
+        <v>1.0791</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>9</v>
@@ -4761,7 +3873,7 @@
         <v>0.1266</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.3241</v>
+        <v>1.3259</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>20</v>
@@ -4773,12 +3885,12 @@
         <v>0.0865</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.904</v>
+        <v>0.9052</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>12</v>
@@ -4793,7 +3905,7 @@
         <v>0.0976</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.9795</v>
+        <v>0.9806</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>27</v>
@@ -4805,12 +3917,12 @@
         <v>0.1148</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1.1523</v>
+        <v>1.1536</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>15</v>
@@ -4822,10 +3934,10 @@
         <v>154</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.0496</v>
+        <v>0.0497</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.552</v>
+        <v>0.5514</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>25</v>
@@ -4837,12 +3949,12 @@
         <v>0.1062</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1.1808</v>
+        <v>1.1793</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>18</v>
@@ -4857,7 +3969,7 @@
         <v>0.173</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.1485</v>
+        <v>1.1477</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>33</v>
@@ -4869,12 +3981,12 @@
         <v>0.1422</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.9441</v>
+        <v>0.9434</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>6</v>
@@ -4883,30 +3995,30 @@
         <v>47</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.1952</v>
+        <v>0.1976</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.2066</v>
+        <v>1.2178</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.1409</v>
+        <v>0.1465</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.8708</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>9</v>
@@ -4915,30 +4027,30 @@
         <v>24</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.1005</v>
+        <v>0.1017</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1.0509</v>
+        <v>1.0648</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.1025</v>
+        <v>0.1066</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1.0719</v>
+        <v>1.1158</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>12</v>
@@ -4947,30 +4059,30 @@
         <v>24</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.102</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.0111</v>
+        <v>1.0243</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.1171</v>
+        <v>0.1118</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1.1752</v>
+        <v>1.1236</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>15</v>
@@ -4979,62 +4091,62 @@
         <v>23</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0.0962</v>
+        <v>0.0974</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.07</v>
+        <v>1.0814</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.0735</v>
+        <v>0.0715</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.8176</v>
+        <v>0.7939</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.1748</v>
+        <v>0.173</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.1607</v>
+        <v>1.1473</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>29</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.1555</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>0.993</v>
+        <v>1.0316</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>6</v>
@@ -5046,10 +4158,10 @@
         <v>222</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.1705</v>
+        <v>0.1706</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.054</v>
+        <v>1.0513</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>31</v>
@@ -5061,12 +4173,12 @@
         <v>0.1806</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.1161</v>
+        <v>1.1132</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>9</v>
@@ -5078,10 +4190,10 @@
         <v>222</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.0611</v>
+        <v>0.061</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.6383</v>
+        <v>0.6391</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>24</v>
@@ -5090,15 +4202,15 @@
         <v>170</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.1373</v>
+        <v>0.1372</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.4351</v>
+        <v>1.437</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>12</v>
@@ -5113,7 +4225,7 @@
         <v>0.0739</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.7418</v>
+        <v>0.7426</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>18</v>
@@ -5125,12 +4237,12 @@
         <v>0.1053</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.0571</v>
+        <v>1.0582</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>15</v>
@@ -5145,7 +4257,7 @@
         <v>0.0817</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9083</v>
+        <v>0.9071</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>17</v>
@@ -5157,12 +4269,12 @@
         <v>0.0991</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>1.1025</v>
+        <v>1.101</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>18</v>
@@ -5177,7 +4289,7 @@
         <v>0.132</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.8762</v>
+        <v>0.8755</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>25</v>
@@ -5189,12 +4301,12 @@
         <v>0.1474</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.9783</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>6</v>
@@ -5209,7 +4321,7 @@
         <v>0.1887</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.1663</v>
+        <v>1.1632</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>27</v>
@@ -5221,12 +4333,12 @@
         <v>0.1203</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.7434</v>
+        <v>0.7415</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>9</v>
@@ -5241,7 +4353,7 @@
         <v>0.0872</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9122</v>
+        <v>0.9134</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>28</v>
@@ -5253,12 +4365,12 @@
         <v>0.12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1.2551</v>
+        <v>1.2567</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>12</v>
@@ -5273,7 +4385,7 @@
         <v>0.0876</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.8791</v>
+        <v>0.88</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>29</v>
@@ -5285,12 +4397,12 @@
         <v>0.1244</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.248</v>
+        <v>1.2494</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>15</v>
@@ -5305,7 +4417,7 @@
         <v>0.1317</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.4644</v>
+        <v>1.4625</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>18</v>
@@ -5317,12 +4429,12 @@
         <v>0.079</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0.8788</v>
+        <v>0.8776</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>18</v>
@@ -5337,7 +4449,7 @@
         <v>0.1147</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.7612</v>
+        <v>0.7607</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>37</v>
@@ -5349,7 +4461,7 @@
         <v>0.1602</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1.0636</v>
+        <v>1.0628</v>
       </c>
     </row>
   </sheetData>
@@ -5369,42 +4481,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -5412,23 +4524,23 @@
         <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -98,13 +98,13 @@
     <t xml:space="preserve">away</t>
   </si>
   <si>
-    <t xml:space="preserve">right_wing 1.26 (off 1.23 x def 1.03): Dominic Young</t>
+    <t xml:space="preserve">right_wing 1.29 (off 1.22 x def 1.06): Dominic Young</t>
   </si>
   <si>
     <t xml:space="preserve">home</t>
   </si>
   <si>
-    <t xml:space="preserve">fullback 1.15 (off 1.02 x def 1.12): James Tedesco; right_centre 1.49 (off 1.08 x def 1.37): Billy Smith</t>
+    <t xml:space="preserve">left_wing 1.14 (off 1.26 x def 0.90): Mark Nawaqanitawase; right_centre 1.56 (off 1.08 x def 1.44): Billy Smith</t>
   </si>
   <si>
     <t xml:space="preserve">match_id</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">Greg Marzhew</t>
   </si>
   <si>
-    <t xml:space="preserve">Greg Marzhew (last 2026-09-20, high_jersey_inferred)</t>
+    <t xml:space="preserve">Greg Marzhew (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Bradman Best</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradman Best (last 2026-09-20, high_jersey_inferred)</t>
+    <t xml:space="preserve">Bradman Best (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Kalyn Ponga</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalyn Ponga (last 2026-09-20, role_not_side_specific)</t>
+    <t xml:space="preserve">Kalyn Ponga (last 2026-10-04, role_not_side_specific)</t>
   </si>
   <si>
     <t xml:space="preserve">cold</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">Dane Gagai</t>
   </si>
   <si>
-    <t xml:space="preserve">Dane Gagai (last 2026-09-20, high_jersey_inferred)</t>
+    <t xml:space="preserve">Dane Gagai (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">positive</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">Dominic Young</t>
   </si>
   <si>
-    <t xml:space="preserve">Dominic Young (last 2026-09-20, high_jersey_inferred)</t>
+    <t xml:space="preserve">Dominic Young (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Mark Nawaqanitawase</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-09-19, high_jersey_inferred)</t>
+    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Robert Toia</t>
   </si>
   <si>
-    <t xml:space="preserve">Robert Toia (last 2026-09-19, high_jersey_inferred)</t>
+    <t xml:space="preserve">Robert Toia (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">James Tedesco</t>
   </si>
   <si>
-    <t xml:space="preserve">James Tedesco (last 2026-09-19, role_not_side_specific)</t>
+    <t xml:space="preserve">James Tedesco (last 2026-10-04, role_not_side_specific)</t>
   </si>
   <si>
     <t xml:space="preserve">strong</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">Billy Smith</t>
   </si>
   <si>
-    <t xml:space="preserve">Billy Smith (last 2026-09-19, high_jersey_inferred)</t>
+    <t xml:space="preserve">Billy Smith (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Daniel Tupou</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel Tupou (last 2026-09-19, high_jersey_inferred)</t>
+    <t xml:space="preserve">Daniel Tupou (last 2026-10-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">team_name</t>
@@ -687,7 +687,7 @@
     <col min="19" max="19" width="9.285" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="12.715" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="89.89" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="95.8925" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -778,49 +778,49 @@
         <v>26</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.56</v>
+        <v>0.52</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -846,49 +846,49 @@
         <v>28</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>1.06</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>1.08</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.72</v>
+        <v>0.69</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>29</v>
@@ -1032,40 +1032,40 @@
         <v>26</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3.7336</v>
+        <v>3.8401</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.1794</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>1.1136</v>
+        <v>1.1033</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1465</v>
+        <v>0.1464</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.903</v>
+        <v>0.9004</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>1.0056</v>
+        <v>0.9934</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.5972</v>
+        <v>0.6095</v>
       </c>
       <c r="T2" s="3" t="s">
         <v>47</v>
@@ -1100,7 +1100,7 @@
         <v>26</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3.7336</v>
+        <v>3.8401</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
@@ -1109,31 +1109,31 @@
         <v>15</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.0839</v>
+        <v>0.081</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.8784</v>
+        <v>0.8487</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.1066</v>
+        <v>0.1078</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>1.1158</v>
+        <v>1.1292</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.9802</v>
+        <v>0.9584</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.3427</v>
+        <v>0.3451</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>47</v>
@@ -1168,40 +1168,40 @@
         <v>26</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3.7336</v>
+        <v>3.8401</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0944</v>
+        <v>0.096</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.9482</v>
+        <v>0.9682</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1118</v>
+        <v>0.1129</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1.1236</v>
+        <v>1.138</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.0654</v>
+        <v>1.1017</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.3881</v>
+        <v>0.4122</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>47</v>
@@ -1236,7 +1236,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3.7336</v>
+        <v>3.8401</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -1245,31 +1245,31 @@
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0632</v>
+        <v>0.061</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.7013</v>
+        <v>0.6774</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>13</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.0715</v>
+        <v>0.0691</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.7939</v>
+        <v>0.7675</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.5568</v>
+        <v>0.5199</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.1766</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>54</v>
@@ -1304,40 +1304,40 @@
         <v>26</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.7336</v>
+        <v>3.8401</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1848</v>
+        <v>0.1834</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.2261</v>
+        <v>1.2154</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1555</v>
+        <v>0.1599</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.0316</v>
+        <v>1.0595</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.2648</v>
+        <v>1.2877</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6979</v>
+        <v>0.7331</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>57</v>
@@ -1372,43 +1372,43 @@
         <v>28</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.1887</v>
+        <v>4.8731</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1976</v>
+        <v>0.2054</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.2178</v>
+        <v>1.2629</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1412</v>
+        <v>0.1465</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.87</v>
+        <v>0.9009</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.0595</v>
+        <v>1.1378</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.9118</v>
+        <v>0.9189</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="U7" s="3" t="s">
         <v>60</v>
@@ -1440,19 +1440,19 @@
         <v>28</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.1887</v>
+        <v>4.8731</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1017</v>
+        <v>0.1016</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1.0648</v>
@@ -1461,19 +1461,19 @@
         <v>14</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0652</v>
+        <v>0.0639</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.6831</v>
+        <v>0.6694</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.7274</v>
+        <v>0.7127</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.3685</v>
+        <v>0.3379</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>54</v>
@@ -1508,7 +1508,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.1887</v>
+        <v>4.8731</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -1517,34 +1517,34 @@
         <v>24</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.102</v>
+        <v>0.098</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.0243</v>
+        <v>0.9885</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1117</v>
+        <v>0.1094</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.1225</v>
+        <v>1.1032</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.1498</v>
+        <v>1.0906</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6071</v>
+        <v>0.5371</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>64</v>
@@ -1576,40 +1576,40 @@
         <v>28</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.1887</v>
+        <v>4.8731</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0974</v>
+        <v>0.0975</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.0814</v>
+        <v>1.0827</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1237</v>
+        <v>0.1294</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.3737</v>
+        <v>1.4372</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.4855</v>
+        <v>1.5561</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.7095</v>
+        <v>0.6957</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>66</v>
@@ -1644,40 +1644,40 @@
         <v>28</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.1887</v>
+        <v>4.8731</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.173</v>
+        <v>0.1702</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.1473</v>
+        <v>1.1277</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.0942</v>
+        <v>0.0922</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6247</v>
+        <v>0.6113</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7167</v>
+        <v>0.6893</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.5731</v>
+        <v>0.5166</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>54</v>
@@ -1761,7 +1761,7 @@
         <v>0.1449</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.8929</v>
+        <v>0.891</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
         <v>0.12</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.7395</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="3">
@@ -1793,7 +1793,7 @@
         <v>0.1179</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.2344</v>
+        <v>1.2351</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>21</v>
@@ -1805,7 +1805,7 @@
         <v>0.0979</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.0255</v>
+        <v>1.0261</v>
       </c>
     </row>
     <row r="4">
@@ -1825,7 +1825,7 @@
         <v>0.1093</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.0981</v>
+        <v>1.1019</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>27</v>
@@ -1837,7 +1837,7 @@
         <v>0.1243</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.2489</v>
+        <v>1.2533</v>
       </c>
     </row>
     <row r="5">
@@ -1857,7 +1857,7 @@
         <v>0.0997</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1076</v>
+        <v>1.1079</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>21</v>
@@ -1869,7 +1869,7 @@
         <v>0.0976</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.0835</v>
+        <v>1.0838</v>
       </c>
     </row>
     <row r="6">
@@ -1889,7 +1889,7 @@
         <v>0.1352</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.8966</v>
+        <v>0.8958</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>37</v>
@@ -1901,7 +1901,7 @@
         <v>0.1714</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.1367</v>
+        <v>1.1356</v>
       </c>
     </row>
     <row r="7">
@@ -1921,7 +1921,7 @@
         <v>0.1254</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.7729</v>
+        <v>0.7713</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>38</v>
@@ -1933,7 +1933,7 @@
         <v>0.1829</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.127</v>
+        <v>1.1247</v>
       </c>
     </row>
     <row r="8">
@@ -1953,7 +1953,7 @@
         <v>0.0743</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7776</v>
+        <v>0.778</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>25</v>
@@ -1965,7 +1965,7 @@
         <v>0.1195</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.2511</v>
+        <v>1.2518</v>
       </c>
     </row>
     <row r="9">
@@ -1982,10 +1982,10 @@
         <v>220</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1212</v>
+        <v>0.1211</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.2172</v>
+        <v>1.2214</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>17</v>
@@ -1994,10 +1994,10 @@
         <v>206</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0838</v>
+        <v>0.0837</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8414</v>
+        <v>0.8442</v>
       </c>
     </row>
     <row r="10">
@@ -2017,7 +2017,7 @@
         <v>0.1078</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.1972</v>
+        <v>1.1974</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>16</v>
@@ -2029,7 +2029,7 @@
         <v>0.0786</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8725</v>
+        <v>0.8726</v>
       </c>
     </row>
     <row r="11">
@@ -2049,7 +2049,7 @@
         <v>0.1119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7424</v>
+        <v>0.7417</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>0.137</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9087</v>
+        <v>0.9079</v>
       </c>
     </row>
     <row r="12">
@@ -2081,7 +2081,7 @@
         <v>0.1357</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8363</v>
+        <v>0.8346</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>38</v>
@@ -2093,7 +2093,7 @@
         <v>0.2082</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.2831</v>
+        <v>1.2804</v>
       </c>
     </row>
     <row r="13">
@@ -2113,7 +2113,7 @@
         <v>0.069</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7226</v>
+        <v>0.723</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>10</v>
@@ -2125,7 +2125,7 @@
         <v>0.0591</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.619</v>
+        <v>0.6193</v>
       </c>
     </row>
     <row r="14">
@@ -2145,7 +2145,7 @@
         <v>0.0642</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6455</v>
+        <v>0.6475</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>12</v>
@@ -2157,7 +2157,7 @@
         <v>0.0697</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7003</v>
+        <v>0.7026</v>
       </c>
     </row>
     <row r="15">
@@ -2177,7 +2177,7 @@
         <v>0.089</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9882</v>
+        <v>0.9884</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
         <v>0.0587</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6516</v>
+        <v>0.6517</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>0.1246</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8262</v>
+        <v>0.8255</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>39</v>
@@ -2221,7 +2221,7 @@
         <v>0.2124</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.4088</v>
+        <v>1.4074</v>
       </c>
     </row>
     <row r="17">
@@ -2238,10 +2238,10 @@
         <v>237</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1446</v>
+        <v>0.1447</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8915</v>
+        <v>0.8896</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>35</v>
@@ -2250,10 +2250,10 @@
         <v>196</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1773</v>
+        <v>0.1774</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.093</v>
+        <v>1.0907</v>
       </c>
     </row>
     <row r="18">
@@ -2273,7 +2273,7 @@
         <v>0.1365</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.4289</v>
+        <v>1.4297</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>15</v>
@@ -2285,7 +2285,7 @@
         <v>0.078</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8163</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="19">
@@ -2305,7 +2305,7 @@
         <v>0.0814</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8177</v>
+        <v>0.8205</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>17</v>
@@ -2317,7 +2317,7 @@
         <v>0.0877</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8811</v>
+        <v>0.8841</v>
       </c>
     </row>
     <row r="20">
@@ -2337,7 +2337,7 @@
         <v>0.061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6778</v>
+        <v>0.6779</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>21</v>
@@ -2349,7 +2349,7 @@
         <v>0.1059</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.1755</v>
+        <v>1.1758</v>
       </c>
     </row>
     <row r="21">
@@ -2369,7 +2369,7 @@
         <v>0.1518</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.0072</v>
+        <v>1.0062</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>34</v>
@@ -2381,7 +2381,7 @@
         <v>0.1718</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.1393</v>
+        <v>1.1383</v>
       </c>
     </row>
     <row r="22">
@@ -2395,25 +2395,25 @@
         <v>36</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1514</v>
+        <v>0.149</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9328</v>
+        <v>0.9165</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.164</v>
+        <v>0.1679</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.0105</v>
+        <v>1.0325</v>
       </c>
     </row>
     <row r="23">
@@ -2424,28 +2424,28 @@
         <v>9</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1315</v>
+        <v>0.1333</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.3766</v>
+        <v>1.3966</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1068</v>
+        <v>0.1079</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.1179</v>
+        <v>1.1306</v>
       </c>
     </row>
     <row r="24">
@@ -2459,25 +2459,25 @@
         <v>38</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1553</v>
+        <v>0.1528</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.5598</v>
+        <v>1.5412</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.0929</v>
+        <v>0.0898</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9329</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="25">
@@ -2491,25 +2491,25 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.0751</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8467</v>
+        <v>0.8338</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.0921</v>
+        <v>0.0892</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.0232</v>
+        <v>0.9906</v>
       </c>
     </row>
     <row r="26">
@@ -2520,28 +2520,28 @@
         <v>18</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1349</v>
+        <v>0.1406</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8952</v>
+        <v>0.9317</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1394</v>
+        <v>0.1395</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9247</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="27">
@@ -2561,7 +2561,7 @@
         <v>0.175</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.0784</v>
+        <v>1.0762</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>39</v>
@@ -2573,7 +2573,7 @@
         <v>0.1606</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9898</v>
+        <v>0.9877</v>
       </c>
     </row>
     <row r="28">
@@ -2593,7 +2593,7 @@
         <v>0.1069</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.1194</v>
+        <v>1.12</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>20</v>
@@ -2605,7 +2605,7 @@
         <v>0.0831</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8703</v>
+        <v>0.8707</v>
       </c>
     </row>
     <row r="29">
@@ -2622,10 +2622,10 @@
         <v>176</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.0448</v>
+        <v>0.0447</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4496</v>
+        <v>0.451</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>24</v>
@@ -2637,7 +2637,7 @@
         <v>0.0988</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9927</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="30">
@@ -2657,7 +2657,7 @@
         <v>0.0908</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.0088</v>
+        <v>1.009</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>26</v>
@@ -2669,7 +2669,7 @@
         <v>0.1059</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.1766</v>
+        <v>1.1769</v>
       </c>
     </row>
     <row r="31">
@@ -2686,10 +2686,10 @@
         <v>176</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1271</v>
+        <v>0.1272</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8434</v>
+        <v>0.8427</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>34</v>
@@ -2701,7 +2701,7 @@
         <v>0.1406</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9326</v>
+        <v>0.9317</v>
       </c>
     </row>
     <row r="32">
@@ -2718,10 +2718,10 @@
         <v>207</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.182</v>
+        <v>0.1821</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.122</v>
+        <v>1.1196</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>31</v>
@@ -2733,7 +2733,7 @@
         <v>0.168</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.0353</v>
+        <v>1.0332</v>
       </c>
     </row>
     <row r="33">
@@ -2753,7 +2753,7 @@
         <v>0.1055</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.1047</v>
+        <v>1.1053</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>15</v>
@@ -2765,7 +2765,7 @@
         <v>0.0826</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8652</v>
+        <v>0.8657</v>
       </c>
     </row>
     <row r="34">
@@ -2785,7 +2785,7 @@
         <v>0.0923</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9277</v>
+        <v>0.9309</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>19</v>
@@ -2794,10 +2794,10 @@
         <v>184</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.103</v>
+        <v>0.1029</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.0344</v>
+        <v>1.0379</v>
       </c>
     </row>
     <row r="35">
@@ -2817,7 +2817,7 @@
         <v>0.15</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.6654</v>
+        <v>1.6657</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>14</v>
@@ -2829,7 +2829,7 @@
         <v>0.0772</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.8574</v>
+        <v>0.8576</v>
       </c>
     </row>
     <row r="36">
@@ -2849,7 +2849,7 @@
         <v>0.1229</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.8154</v>
+        <v>0.8147</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>29</v>
@@ -2861,7 +2861,7 @@
         <v>0.1571</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.0419</v>
+        <v>1.0409</v>
       </c>
     </row>
     <row r="37">
@@ -2881,7 +2881,7 @@
         <v>0.1657</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.0214</v>
+        <v>1.0192</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>38</v>
@@ -2893,7 +2893,7 @@
         <v>0.1888</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1637</v>
+        <v>1.1613</v>
       </c>
     </row>
     <row r="38">
@@ -2913,7 +2913,7 @@
         <v>0.0778</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.8146</v>
+        <v>0.815</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>21</v>
@@ -2925,7 +2925,7 @@
         <v>0.1048</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.0971</v>
+        <v>1.0977</v>
       </c>
     </row>
     <row r="39">
@@ -2942,10 +2942,10 @@
         <v>235</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.1498</v>
+        <v>0.1497</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.5046</v>
+        <v>1.51</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>0.0818</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.822</v>
+        <v>0.8248</v>
       </c>
     </row>
     <row r="40">
@@ -2977,7 +2977,7 @@
         <v>0.0535</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.5947</v>
+        <v>0.5948</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>18</v>
@@ -2989,7 +2989,7 @@
         <v>0.0904</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0044</v>
       </c>
     </row>
     <row r="41">
@@ -3009,7 +3009,7 @@
         <v>0.1451</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.9623</v>
+        <v>0.9614</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>36</v>
@@ -3021,7 +3021,7 @@
         <v>0.1787</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.1852</v>
+        <v>1.184</v>
       </c>
     </row>
     <row r="42">
@@ -3032,28 +3032,28 @@
         <v>6</v>
       </c>
       <c r="C42" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1.1033</v>
+      </c>
+      <c r="G42" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D42" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0.1807</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>1.1136</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="H42" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.1412</v>
+        <v>0.1465</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.87</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="43">
@@ -3067,25 +3067,25 @@
         <v>15</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.0839</v>
+        <v>0.081</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.8784</v>
+        <v>0.8487</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.0652</v>
+        <v>0.0639</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.6831</v>
+        <v>0.6694</v>
       </c>
     </row>
     <row r="44">
@@ -3096,28 +3096,28 @@
         <v>12</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.0944</v>
+        <v>0.096</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.9482</v>
+        <v>0.9682</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>25</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.1117</v>
+        <v>0.1094</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.1225</v>
+        <v>1.1032</v>
       </c>
     </row>
     <row r="45">
@@ -3131,25 +3131,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.0632</v>
+        <v>0.061</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.7013</v>
+        <v>0.6774</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.1237</v>
+        <v>0.1294</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.3737</v>
+        <v>1.4372</v>
       </c>
     </row>
     <row r="46">
@@ -3160,28 +3160,28 @@
         <v>18</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.1848</v>
+        <v>0.1834</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.2261</v>
+        <v>1.2154</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>0.0942</v>
+        <v>0.0922</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6247</v>
+        <v>0.6113</v>
       </c>
     </row>
     <row r="47">
@@ -3198,10 +3198,10 @@
         <v>197</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.1624</v>
+        <v>0.1625</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.001</v>
+        <v>0.999</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>50</v>
@@ -3213,7 +3213,7 @@
         <v>0.2063</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.2712</v>
+        <v>1.2685</v>
       </c>
     </row>
     <row r="48">
@@ -3233,7 +3233,7 @@
         <v>0.0823</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.8616</v>
+        <v>0.8621</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>22</v>
@@ -3245,7 +3245,7 @@
         <v>0.0923</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.966</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="49">
@@ -3262,10 +3262,10 @@
         <v>197</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.106</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.0656</v>
+        <v>1.0693</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>23</v>
@@ -3277,7 +3277,7 @@
         <v>0.0964</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.9689</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="50">
@@ -3294,10 +3294,10 @@
         <v>197</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1101</v>
+        <v>0.11</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.2222</v>
+        <v>1.2224</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>19</v>
@@ -3309,7 +3309,7 @@
         <v>0.0802</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.8902</v>
+        <v>0.8904</v>
       </c>
     </row>
     <row r="51">
@@ -3329,7 +3329,7 @@
         <v>0.1569</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.0406</v>
+        <v>1.0396</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>33</v>
@@ -3341,7 +3341,7 @@
         <v>0.1389</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.9212</v>
+        <v>0.9203</v>
       </c>
     </row>
     <row r="52">
@@ -3361,7 +3361,7 @@
         <v>0.1526</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9402</v>
+        <v>0.9383</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>29</v>
@@ -3373,7 +3373,7 @@
         <v>0.1356</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.8358</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="53">
@@ -3393,7 +3393,7 @@
         <v>0.0749</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.7841</v>
+        <v>0.7845</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>24</v>
@@ -3405,7 +3405,7 @@
         <v>0.1096</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.1471</v>
+        <v>1.1477</v>
       </c>
     </row>
     <row r="54">
@@ -3422,10 +3422,10 @@
         <v>178</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.1165</v>
+        <v>0.1164</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.17</v>
+        <v>1.174</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>13</v>
@@ -3437,7 +3437,7 @@
         <v>0.0626</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.6292</v>
+        <v>0.6313</v>
       </c>
     </row>
     <row r="55">
@@ -3457,7 +3457,7 @@
         <v>0.0951</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.0556</v>
+        <v>1.0559</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>18</v>
@@ -3469,7 +3469,7 @@
         <v>0.0834</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.9266</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="56">
@@ -3489,7 +3489,7 @@
         <v>0.1207</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.8005</v>
+        <v>0.7998</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>40</v>
@@ -3501,7 +3501,7 @@
         <v>0.182</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.2075</v>
+        <v>1.2063</v>
       </c>
     </row>
     <row r="57">
@@ -3515,25 +3515,25 @@
         <v>36</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.1532</v>
+        <v>0.152</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.9439</v>
+        <v>0.9346</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.1537</v>
+        <v>0.1503</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0.9475</v>
+        <v>0.9242</v>
       </c>
     </row>
     <row r="58">
@@ -3547,25 +3547,25 @@
         <v>31</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.1291</v>
+        <v>0.1281</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.3515</v>
+        <v>1.3416</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.0898</v>
+        <v>0.0877</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.9398</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="59">
@@ -3579,25 +3579,25 @@
         <v>22</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.0936</v>
+        <v>0.0929</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.9405</v>
+        <v>0.9364</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.0844</v>
+        <v>0.0824</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.8474</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="60">
@@ -3608,28 +3608,28 @@
         <v>15</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.0573</v>
+        <v>0.0608</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.6364</v>
+        <v>0.6752</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.1124</v>
+        <v>0.1098</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.248</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="61">
@@ -3643,25 +3643,25 @@
         <v>50</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.208</v>
+        <v>0.2064</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.3797</v>
+        <v>1.3675</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0.1006</v>
+        <v>0.104</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.6677</v>
+        <v>0.6894</v>
       </c>
     </row>
     <row r="62">
@@ -3681,7 +3681,7 @@
         <v>0.1366</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.8418</v>
+        <v>0.8401</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>28</v>
@@ -3693,7 +3693,7 @@
         <v>0.1378</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.8494</v>
+        <v>0.8477</v>
       </c>
     </row>
     <row r="63">
@@ -3713,7 +3713,7 @@
         <v>0.047</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.4921</v>
+        <v>0.4923</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>18</v>
@@ -3725,7 +3725,7 @@
         <v>0.088</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.921</v>
+        <v>0.9215</v>
       </c>
     </row>
     <row r="64">
@@ -3745,7 +3745,7 @@
         <v>0.0785</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.789</v>
+        <v>0.7917</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>27</v>
@@ -3757,7 +3757,7 @@
         <v>0.1288</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1.2939</v>
+        <v>1.2985</v>
       </c>
     </row>
     <row r="65">
@@ -3777,7 +3777,7 @@
         <v>0.127</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.41</v>
+        <v>1.4103</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>13</v>
@@ -3789,7 +3789,7 @@
         <v>0.065</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.7224</v>
+        <v>0.7225</v>
       </c>
     </row>
     <row r="66">
@@ -3809,7 +3809,7 @@
         <v>0.234</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.5521</v>
+        <v>1.5506</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>28</v>
@@ -3821,7 +3821,7 @@
         <v>0.137</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.9087</v>
+        <v>0.9079</v>
       </c>
     </row>
     <row r="67">
@@ -3841,7 +3841,7 @@
         <v>0.2094</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.2905</v>
+        <v>1.2878</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>41</v>
@@ -3853,7 +3853,7 @@
         <v>0.1751</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.0791</v>
+        <v>1.0768</v>
       </c>
     </row>
     <row r="68">
@@ -3873,7 +3873,7 @@
         <v>0.1266</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.3259</v>
+        <v>1.3266</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>20</v>
@@ -3885,7 +3885,7 @@
         <v>0.0865</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.9052</v>
+        <v>0.9057</v>
       </c>
     </row>
     <row r="69">
@@ -3905,7 +3905,7 @@
         <v>0.0976</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.9806</v>
+        <v>0.9838</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>27</v>
@@ -3917,7 +3917,7 @@
         <v>0.1148</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1.1536</v>
+        <v>1.1577</v>
       </c>
     </row>
     <row r="70">
@@ -3934,10 +3934,10 @@
         <v>154</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.0497</v>
+        <v>0.0496</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.5514</v>
+        <v>0.5515</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>25</v>
@@ -3949,7 +3949,7 @@
         <v>0.1062</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1.1793</v>
+        <v>1.1795</v>
       </c>
     </row>
     <row r="71">
@@ -3969,7 +3969,7 @@
         <v>0.173</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.1477</v>
+        <v>1.1466</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>33</v>
@@ -3981,7 +3981,7 @@
         <v>0.1422</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.9434</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="72">
@@ -3992,28 +3992,28 @@
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.1976</v>
+        <v>0.2054</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.2178</v>
+        <v>1.2629</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.1465</v>
+        <v>0.1464</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.903</v>
+        <v>0.9004</v>
       </c>
     </row>
     <row r="73">
@@ -4024,28 +4024,28 @@
         <v>9</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.1017</v>
+        <v>0.1016</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>1.0648</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.1066</v>
+        <v>0.1078</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1.1158</v>
+        <v>1.1292</v>
       </c>
     </row>
     <row r="74">
@@ -4059,25 +4059,25 @@
         <v>24</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.102</v>
+        <v>0.098</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.0243</v>
+        <v>0.9885</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.1118</v>
+        <v>0.1129</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1.1236</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="75">
@@ -4088,28 +4088,28 @@
         <v>15</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0.0974</v>
+        <v>0.0975</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.0814</v>
+        <v>1.0827</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.0715</v>
+        <v>0.0691</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.7939</v>
+        <v>0.7675</v>
       </c>
     </row>
     <row r="76">
@@ -4120,28 +4120,28 @@
         <v>18</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.173</v>
+        <v>0.1702</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.1473</v>
+        <v>1.1277</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.1555</v>
+        <v>0.1599</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>1.0316</v>
+        <v>1.0595</v>
       </c>
     </row>
     <row r="77">
@@ -4161,7 +4161,7 @@
         <v>0.1706</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.0513</v>
+        <v>1.0491</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>31</v>
@@ -4170,10 +4170,10 @@
         <v>170</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.1806</v>
+        <v>0.1807</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.1132</v>
+        <v>1.1109</v>
       </c>
     </row>
     <row r="78">
@@ -4193,7 +4193,7 @@
         <v>0.061</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.6391</v>
+        <v>0.6394</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>24</v>
@@ -4205,7 +4205,7 @@
         <v>0.1372</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.437</v>
+        <v>1.4378</v>
       </c>
     </row>
     <row r="79">
@@ -4225,7 +4225,7 @@
         <v>0.0739</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.7426</v>
+        <v>0.7451</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>18</v>
@@ -4237,7 +4237,7 @@
         <v>0.1053</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.0582</v>
+        <v>1.0619</v>
       </c>
     </row>
     <row r="80">
@@ -4257,7 +4257,7 @@
         <v>0.0817</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9071</v>
+        <v>0.9073</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>17</v>
@@ -4269,7 +4269,7 @@
         <v>0.0991</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>1.101</v>
+        <v>1.1013</v>
       </c>
     </row>
     <row r="81">
@@ -4289,7 +4289,7 @@
         <v>0.132</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.8755</v>
+        <v>0.8747</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>25</v>
@@ -4301,7 +4301,7 @@
         <v>0.1474</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.9776</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="82">
@@ -4318,10 +4318,10 @@
         <v>162</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0.1887</v>
+        <v>0.1888</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.1632</v>
+        <v>1.1608</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>27</v>
@@ -4333,7 +4333,7 @@
         <v>0.1203</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.7415</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="83">
@@ -4353,7 +4353,7 @@
         <v>0.0872</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9134</v>
+        <v>0.9138</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>28</v>
@@ -4365,7 +4365,7 @@
         <v>0.12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1.2567</v>
+        <v>1.2574</v>
       </c>
     </row>
     <row r="84">
@@ -4385,7 +4385,7 @@
         <v>0.0876</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.88</v>
+        <v>0.883</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>29</v>
@@ -4394,10 +4394,10 @@
         <v>230</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0.1244</v>
+        <v>0.1243</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.2494</v>
+        <v>1.2538</v>
       </c>
     </row>
     <row r="85">
@@ -4417,7 +4417,7 @@
         <v>0.1317</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.4625</v>
+        <v>1.4628</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>18</v>
@@ -4429,7 +4429,7 @@
         <v>0.079</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0.8776</v>
+        <v>0.8778</v>
       </c>
     </row>
     <row r="86">
@@ -4449,7 +4449,7 @@
         <v>0.1147</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.7607</v>
+        <v>0.76</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>37</v>
@@ -4461,7 +4461,7 @@
         <v>0.1602</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1.0628</v>
+        <v>1.0618</v>
       </c>
     </row>
   </sheetData>
